--- a/MerapiHotspot-2000-14.xlsx
+++ b/MerapiHotspot-2000-14.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALL\KerjaPraktik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kerja Praktik\modisss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4764C202-A001-47AC-A858-F1687D3469F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00E0D47-6469-428E-A99E-93C274C50E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -265,7 +265,7 @@
     <numFmt numFmtId="165" formatCode="d/m/yy\ h:mm;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +277,26 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -311,10 +331,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -325,6 +344,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -345,7 +368,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="id-ID"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -491,7 +514,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="id-ID"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -643,7 +666,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="id-ID"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -979,7 +1002,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="id-ID"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -28383,37 +28406,37 @@
         <f>(A372+2209125600)/86400</f>
         <v>46264.385416666664</v>
       </c>
-      <c r="I372" s="9">
+      <c r="I372" s="8">
         <v>127.633728</v>
       </c>
-      <c r="J372" s="9">
+      <c r="J372" s="8">
         <v>1.499201</v>
       </c>
-      <c r="K372" s="9">
+      <c r="K372" s="8">
         <v>0.81599999999999995</v>
       </c>
-      <c r="L372" s="9">
+      <c r="L372" s="8">
         <v>0.77600000000000002</v>
       </c>
-      <c r="M372" s="9">
+      <c r="M372" s="8">
         <v>173.809</v>
       </c>
-      <c r="N372" s="9">
+      <c r="N372" s="8">
         <v>7.0720000000000001</v>
       </c>
-      <c r="O372" s="9">
+      <c r="O372" s="8">
         <v>6.4059999999999997</v>
       </c>
-      <c r="P372" s="9">
+      <c r="P372" s="8">
         <v>22.8</v>
       </c>
-      <c r="Q372" s="9">
+      <c r="Q372" s="8">
         <v>-81.88</v>
       </c>
-      <c r="R372" s="9">
+      <c r="R372" s="8">
         <v>122.21</v>
       </c>
-      <c r="S372" s="9">
+      <c r="S372" s="8">
         <v>78.48</v>
       </c>
       <c r="T372">
@@ -28422,19 +28445,19 @@
       <c r="U372">
         <v>929</v>
       </c>
-      <c r="V372" s="9">
+      <c r="V372" s="8">
         <v>-0.78</v>
       </c>
-      <c r="W372" s="9">
+      <c r="W372" s="8">
         <v>100.761</v>
       </c>
-      <c r="X372" s="9">
+      <c r="X372" s="8">
         <v>5.476</v>
       </c>
-      <c r="Y372" s="9">
+      <c r="Y372" s="8">
         <v>292.2</v>
       </c>
-      <c r="Z372" s="9">
+      <c r="Z372" s="8">
         <v>1.9</v>
       </c>
     </row>
@@ -28464,37 +28487,37 @@
         <f t="shared" si="5"/>
         <v>46264.093738425923</v>
       </c>
-      <c r="I373" s="9">
+      <c r="I373" s="8">
         <v>127.63200399999999</v>
       </c>
-      <c r="J373" s="9">
+      <c r="J373" s="8">
         <v>1.499104</v>
       </c>
-      <c r="K373" s="9">
+      <c r="K373" s="8">
         <v>0.89600000000000002</v>
       </c>
-      <c r="L373" s="9">
+      <c r="L373" s="8">
         <v>0.97899999999999998</v>
       </c>
-      <c r="M373" s="9">
+      <c r="M373" s="8">
         <v>181.31299999999999</v>
       </c>
-      <c r="N373" s="9">
+      <c r="N373" s="8">
         <v>8.3970000000000002</v>
       </c>
-      <c r="O373" s="9">
+      <c r="O373" s="8">
         <v>7.8209999999999997</v>
       </c>
-      <c r="P373" s="9">
+      <c r="P373" s="8">
         <v>22.98</v>
       </c>
-      <c r="Q373" s="9">
+      <c r="Q373" s="8">
         <v>-97.69</v>
       </c>
-      <c r="R373" s="9">
+      <c r="R373" s="8">
         <v>131.44</v>
       </c>
-      <c r="S373" s="9">
+      <c r="S373" s="8">
         <v>-76.75</v>
       </c>
       <c r="T373">
@@ -28503,19 +28526,19 @@
       <c r="U373">
         <v>423</v>
       </c>
-      <c r="V373" s="9">
+      <c r="V373" s="8">
         <v>-0.78</v>
       </c>
-      <c r="W373" s="9">
+      <c r="W373" s="8">
         <v>151.381</v>
       </c>
-      <c r="X373" s="9">
+      <c r="X373" s="8">
         <v>8.9760000000000009</v>
       </c>
-      <c r="Y373" s="9">
+      <c r="Y373" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z373" s="9">
+      <c r="Z373" s="8">
         <v>3.4</v>
       </c>
     </row>
@@ -28545,37 +28568,37 @@
         <f t="shared" si="5"/>
         <v>46259.097222222219</v>
       </c>
-      <c r="I374" s="9">
+      <c r="I374" s="8">
         <v>127.635643</v>
       </c>
-      <c r="J374" s="9">
+      <c r="J374" s="8">
         <v>1.500283</v>
       </c>
-      <c r="K374" s="9">
+      <c r="K374" s="8">
         <v>1.0409999999999999</v>
       </c>
-      <c r="L374" s="9">
+      <c r="L374" s="8">
         <v>0.996</v>
       </c>
-      <c r="M374" s="9">
+      <c r="M374" s="8">
         <v>181.30600000000001</v>
       </c>
-      <c r="N374" s="9">
+      <c r="N374" s="8">
         <v>8.3889999999999993</v>
       </c>
-      <c r="O374" s="9">
+      <c r="O374" s="8">
         <v>7.9790000000000001</v>
       </c>
-      <c r="P374" s="9">
+      <c r="P374" s="8">
         <v>24.81</v>
       </c>
-      <c r="Q374" s="9">
+      <c r="Q374" s="8">
         <v>-98.78</v>
       </c>
-      <c r="R374" s="9">
+      <c r="R374" s="8">
         <v>131.09</v>
       </c>
-      <c r="S374" s="9">
+      <c r="S374" s="8">
         <v>-74.25</v>
       </c>
       <c r="T374">
@@ -28584,19 +28607,19 @@
       <c r="U374">
         <v>403</v>
       </c>
-      <c r="V374" s="9">
+      <c r="V374" s="8">
         <v>-0.78</v>
       </c>
-      <c r="W374" s="9">
+      <c r="W374" s="8">
         <v>152.41499999999999</v>
       </c>
-      <c r="X374" s="9">
+      <c r="X374" s="8">
         <v>9.2970000000000006</v>
       </c>
-      <c r="Y374" s="9">
+      <c r="Y374" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z374" s="9">
+      <c r="Z374" s="8">
         <v>3.4</v>
       </c>
     </row>
@@ -28626,37 +28649,37 @@
         <f t="shared" si="5"/>
         <v>46256.083333333336</v>
       </c>
-      <c r="I375" s="9">
+      <c r="I375" s="8">
         <v>127.632774</v>
       </c>
-      <c r="J375" s="9">
+      <c r="J375" s="8">
         <v>1.492021</v>
       </c>
-      <c r="K375" s="9">
+      <c r="K375" s="8">
         <v>1.57</v>
       </c>
-      <c r="L375" s="9">
+      <c r="L375" s="8">
         <v>1.56</v>
       </c>
-      <c r="M375" s="9">
+      <c r="M375" s="8">
         <v>181.30099999999999</v>
       </c>
-      <c r="N375" s="9">
+      <c r="N375" s="8">
         <v>8.5760000000000005</v>
       </c>
-      <c r="O375" s="9">
+      <c r="O375" s="8">
         <v>8.0269999999999992</v>
       </c>
-      <c r="P375" s="9">
+      <c r="P375" s="8">
         <v>21.26</v>
       </c>
-      <c r="Q375" s="9">
+      <c r="Q375" s="8">
         <v>83.02</v>
       </c>
-      <c r="R375" s="9">
+      <c r="R375" s="8">
         <v>126.17</v>
       </c>
-      <c r="S375" s="9">
+      <c r="S375" s="8">
         <v>-74.23</v>
       </c>
       <c r="T375">
@@ -28665,19 +28688,19 @@
       <c r="U375">
         <v>912</v>
       </c>
-      <c r="V375" s="9">
+      <c r="V375" s="8">
         <v>-0.67</v>
       </c>
-      <c r="W375" s="9">
+      <c r="W375" s="8">
         <v>106.254</v>
       </c>
-      <c r="X375" s="9">
+      <c r="X375" s="8">
         <v>19.956</v>
       </c>
-      <c r="Y375" s="9">
+      <c r="Y375" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z375" s="9">
+      <c r="Z375" s="8">
         <v>3.4</v>
       </c>
     </row>
@@ -28707,37 +28730,37 @@
         <f t="shared" si="5"/>
         <v>46256.083333333336</v>
       </c>
-      <c r="I376" s="9">
+      <c r="I376" s="8">
         <v>127.625015</v>
       </c>
-      <c r="J376" s="9">
+      <c r="J376" s="8">
         <v>1.4975940000000001</v>
       </c>
-      <c r="K376" s="9">
+      <c r="K376" s="8">
         <v>0.89600000000000002</v>
       </c>
-      <c r="L376" s="9">
+      <c r="L376" s="8">
         <v>1.08</v>
       </c>
-      <c r="M376" s="9">
+      <c r="M376" s="8">
         <v>181.30099999999999</v>
       </c>
-      <c r="N376" s="9">
+      <c r="N376" s="8">
         <v>8.4909999999999997</v>
       </c>
-      <c r="O376" s="9">
+      <c r="O376" s="8">
         <v>7.9130000000000003</v>
       </c>
-      <c r="P376" s="9">
+      <c r="P376" s="8">
         <v>21.26</v>
       </c>
-      <c r="Q376" s="9">
+      <c r="Q376" s="8">
         <v>80.84</v>
       </c>
-      <c r="R376" s="9">
+      <c r="R376" s="8">
         <v>126.17</v>
       </c>
-      <c r="S376" s="9">
+      <c r="S376" s="8">
         <v>-74.23</v>
       </c>
       <c r="T376">
@@ -28746,19 +28769,19 @@
       <c r="U376">
         <v>912</v>
       </c>
-      <c r="V376" s="9">
+      <c r="V376" s="8">
         <v>-0.76</v>
       </c>
-      <c r="W376" s="9">
+      <c r="W376" s="8">
         <v>106.514</v>
       </c>
-      <c r="X376" s="9">
+      <c r="X376" s="8">
         <v>10.884</v>
       </c>
-      <c r="Y376" s="9">
+      <c r="Y376" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z376" s="9">
+      <c r="Z376" s="8">
         <v>3.4</v>
       </c>
     </row>
@@ -28788,37 +28811,37 @@
         <f t="shared" si="5"/>
         <v>46253.368043981478</v>
       </c>
-      <c r="I377" s="9">
+      <c r="I377" s="8">
         <v>127.62824999999999</v>
       </c>
-      <c r="J377" s="9">
+      <c r="J377" s="8">
         <v>1.4963679999999999</v>
       </c>
-      <c r="K377" s="9">
+      <c r="K377" s="8">
         <v>1.5269999999999999</v>
       </c>
-      <c r="L377" s="9">
+      <c r="L377" s="8">
         <v>1.45</v>
       </c>
-      <c r="M377" s="9">
+      <c r="M377" s="8">
         <v>173.80199999999999</v>
       </c>
-      <c r="N377" s="9">
+      <c r="N377" s="8">
         <v>8.2539999999999996</v>
       </c>
-      <c r="O377" s="9">
+      <c r="O377" s="8">
         <v>7.726</v>
       </c>
-      <c r="P377" s="9">
+      <c r="P377" s="8">
         <v>32.26</v>
       </c>
-      <c r="Q377" s="9">
+      <c r="Q377" s="8">
         <v>98.78</v>
       </c>
-      <c r="R377" s="9">
+      <c r="R377" s="8">
         <v>128.34</v>
       </c>
-      <c r="S377" s="9">
+      <c r="S377" s="8">
         <v>72.45</v>
       </c>
       <c r="T377">
@@ -28827,19 +28850,19 @@
       <c r="U377">
         <v>322</v>
       </c>
-      <c r="V377" s="9">
+      <c r="V377" s="8">
         <v>-0.68</v>
       </c>
-      <c r="W377" s="9">
+      <c r="W377" s="8">
         <v>154.35</v>
       </c>
-      <c r="X377" s="9">
+      <c r="X377" s="8">
         <v>18.215</v>
       </c>
-      <c r="Y377" s="9">
+      <c r="Y377" s="8">
         <v>292.2</v>
       </c>
-      <c r="Z377" s="9">
+      <c r="Z377" s="8">
         <v>1.9</v>
       </c>
     </row>
@@ -28869,37 +28892,37 @@
         <f t="shared" si="5"/>
         <v>46244.097222222219</v>
       </c>
-      <c r="I378" s="9">
+      <c r="I378" s="8">
         <v>127.63108099999999</v>
       </c>
-      <c r="J378" s="9">
+      <c r="J378" s="8">
         <v>1.4893339999999999</v>
       </c>
-      <c r="K378" s="9">
+      <c r="K378" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="L378" s="9">
+      <c r="L378" s="8">
         <v>1.1140000000000001</v>
       </c>
-      <c r="M378" s="9">
+      <c r="M378" s="8">
         <v>181.28399999999999</v>
       </c>
-      <c r="N378" s="9">
+      <c r="N378" s="8">
         <v>8.4339999999999993</v>
       </c>
-      <c r="O378" s="9">
+      <c r="O378" s="8">
         <v>7.8570000000000002</v>
       </c>
-      <c r="P378" s="9">
+      <c r="P378" s="8">
         <v>29.79</v>
       </c>
-      <c r="Q378" s="9">
+      <c r="Q378" s="8">
         <v>-98.26</v>
       </c>
-      <c r="R378" s="9">
+      <c r="R378" s="8">
         <v>130.12</v>
       </c>
-      <c r="S378" s="9">
+      <c r="S378" s="8">
         <v>-68.37</v>
       </c>
       <c r="T378">
@@ -28908,19 +28931,19 @@
       <c r="U378">
         <v>349</v>
       </c>
-      <c r="V378" s="9">
+      <c r="V378" s="8">
         <v>-0.75</v>
       </c>
-      <c r="W378" s="9">
+      <c r="W378" s="8">
         <v>152.13999999999999</v>
       </c>
-      <c r="X378" s="9">
+      <c r="X378" s="8">
         <v>11.526999999999999</v>
       </c>
-      <c r="Y378" s="9">
+      <c r="Y378" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z378" s="9">
+      <c r="Z378" s="8">
         <v>3.4</v>
       </c>
     </row>
@@ -28950,37 +28973,37 @@
         <f t="shared" si="5"/>
         <v>46244.097222222219</v>
       </c>
-      <c r="I379" s="9">
+      <c r="I379" s="8">
         <v>127.630211</v>
       </c>
-      <c r="J379" s="9">
+      <c r="J379" s="8">
         <v>1.4993559999999999</v>
       </c>
-      <c r="K379" s="9">
+      <c r="K379" s="8">
         <v>1.976</v>
       </c>
-      <c r="L379" s="9">
+      <c r="L379" s="8">
         <v>1.956</v>
       </c>
-      <c r="M379" s="9">
+      <c r="M379" s="8">
         <v>181.28399999999999</v>
       </c>
-      <c r="N379" s="9">
+      <c r="N379" s="8">
         <v>8.6389999999999993</v>
       </c>
-      <c r="O379" s="9">
+      <c r="O379" s="8">
         <v>8.0370000000000008</v>
       </c>
-      <c r="P379" s="9">
+      <c r="P379" s="8">
         <v>29.79</v>
       </c>
-      <c r="Q379" s="9">
+      <c r="Q379" s="8">
         <v>-98.43</v>
       </c>
-      <c r="R379" s="9">
+      <c r="R379" s="8">
         <v>130.12</v>
       </c>
-      <c r="S379" s="9">
+      <c r="S379" s="8">
         <v>-68.37</v>
       </c>
       <c r="T379">
@@ -28989,19 +29012,19 @@
       <c r="U379">
         <v>349</v>
       </c>
-      <c r="V379" s="9">
+      <c r="V379" s="8">
         <v>-0.61</v>
       </c>
-      <c r="W379" s="9">
+      <c r="W379" s="8">
         <v>152.06299999999999</v>
       </c>
-      <c r="X379" s="9">
+      <c r="X379" s="8">
         <v>27.440999999999999</v>
       </c>
-      <c r="Y379" s="9">
+      <c r="Y379" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z379" s="9">
+      <c r="Z379" s="8">
         <v>3.4</v>
       </c>
     </row>
@@ -29031,37 +29054,37 @@
         <f t="shared" si="5"/>
         <v>46243.378472222219</v>
       </c>
-      <c r="I380" s="9">
+      <c r="I380" s="8">
         <v>127.635139</v>
       </c>
-      <c r="J380" s="9">
+      <c r="J380" s="8">
         <v>1.497069</v>
       </c>
-      <c r="K380" s="9">
+      <c r="K380" s="8">
         <v>0.89600000000000002</v>
       </c>
-      <c r="L380" s="9">
+      <c r="L380" s="8">
         <v>0.879</v>
       </c>
-      <c r="M380" s="9">
+      <c r="M380" s="8">
         <v>173.79499999999999</v>
       </c>
-      <c r="N380" s="9">
+      <c r="N380" s="8">
         <v>6.9749999999999996</v>
       </c>
-      <c r="O380" s="9">
+      <c r="O380" s="8">
         <v>6.1340000000000003</v>
       </c>
-      <c r="P380" s="9">
+      <c r="P380" s="8">
         <v>0.28999999999999998</v>
       </c>
-      <c r="Q380" s="9">
+      <c r="Q380" s="8">
         <v>-74.48</v>
       </c>
-      <c r="R380" s="9">
+      <c r="R380" s="8">
         <v>125.13</v>
       </c>
-      <c r="S380" s="9">
+      <c r="S380" s="8">
         <v>69.569999999999993</v>
       </c>
       <c r="T380">
@@ -29070,19 +29093,19 @@
       <c r="U380">
         <v>680</v>
       </c>
-      <c r="V380" s="9">
+      <c r="V380" s="8">
         <v>-0.75</v>
       </c>
-      <c r="W380" s="9">
+      <c r="W380" s="8">
         <v>124.596</v>
       </c>
-      <c r="X380" s="9">
+      <c r="X380" s="8">
         <v>7.423</v>
       </c>
-      <c r="Y380" s="9">
+      <c r="Y380" s="8">
         <v>292.2</v>
       </c>
-      <c r="Z380" s="9">
+      <c r="Z380" s="8">
         <v>1.9</v>
       </c>
     </row>
@@ -29112,37 +29135,37 @@
         <f t="shared" si="5"/>
         <v>46241.086793981478</v>
       </c>
-      <c r="I381" s="9">
+      <c r="I381" s="8">
         <v>127.625519</v>
       </c>
-      <c r="J381" s="9">
+      <c r="J381" s="8">
         <v>1.4941960000000001</v>
       </c>
-      <c r="K381" s="9">
+      <c r="K381" s="8">
         <v>0.83</v>
       </c>
-      <c r="L381" s="9">
+      <c r="L381" s="8">
         <v>0.89600000000000002</v>
       </c>
-      <c r="M381" s="9">
+      <c r="M381" s="8">
         <v>181.28100000000001</v>
       </c>
-      <c r="N381" s="9">
+      <c r="N381" s="8">
         <v>8.4670000000000005</v>
       </c>
-      <c r="O381" s="9">
+      <c r="O381" s="8">
         <v>7.9</v>
       </c>
-      <c r="P381" s="9">
+      <c r="P381" s="8">
         <v>15.7</v>
       </c>
-      <c r="Q381" s="9">
+      <c r="Q381" s="8">
         <v>83.42</v>
       </c>
-      <c r="R381" s="9">
+      <c r="R381" s="8">
         <v>125.42</v>
       </c>
-      <c r="S381" s="9">
+      <c r="S381" s="8">
         <v>-68.510000000000005</v>
       </c>
       <c r="T381">
@@ -29151,19 +29174,19 @@
       <c r="U381">
         <v>851</v>
       </c>
-      <c r="V381" s="9">
+      <c r="V381" s="8">
         <v>-0.8</v>
       </c>
-      <c r="W381" s="9">
+      <c r="W381" s="8">
         <v>111.527</v>
       </c>
-      <c r="X381" s="9">
+      <c r="X381" s="8">
         <v>7.407</v>
       </c>
-      <c r="Y381" s="9">
+      <c r="Y381" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z381" s="9">
+      <c r="Z381" s="8">
         <v>3.4</v>
       </c>
     </row>
@@ -29193,37 +29216,37 @@
         <f t="shared" si="5"/>
         <v>46239.100682870368</v>
       </c>
-      <c r="I382" s="9">
+      <c r="I382" s="8">
         <v>127.631805</v>
       </c>
-      <c r="J382" s="9">
+      <c r="J382" s="8">
         <v>1.4973860000000001</v>
       </c>
-      <c r="K382" s="9">
+      <c r="K382" s="8">
         <v>1.1479999999999999</v>
       </c>
-      <c r="L382" s="9">
+      <c r="L382" s="8">
         <v>1.224</v>
       </c>
-      <c r="M382" s="9">
+      <c r="M382" s="8">
         <v>181.27799999999999</v>
       </c>
-      <c r="N382" s="9">
+      <c r="N382" s="8">
         <v>8.6120000000000001</v>
       </c>
-      <c r="O382" s="9">
+      <c r="O382" s="8">
         <v>8.0519999999999996</v>
       </c>
-      <c r="P382" s="9">
+      <c r="P382" s="8">
         <v>31.4</v>
       </c>
-      <c r="Q382" s="9">
+      <c r="Q382" s="8">
         <v>-97.35</v>
       </c>
-      <c r="R382" s="9">
+      <c r="R382" s="8">
         <v>129.88999999999999</v>
       </c>
-      <c r="S382" s="9">
+      <c r="S382" s="8">
         <v>-66.239999999999995</v>
       </c>
       <c r="T382">
@@ -29232,19 +29255,19 @@
       <c r="U382">
         <v>332</v>
       </c>
-      <c r="V382" s="9">
+      <c r="V382" s="8">
         <v>-0.74</v>
       </c>
-      <c r="W382" s="9">
+      <c r="W382" s="8">
         <v>152.96600000000001</v>
       </c>
-      <c r="X382" s="9">
+      <c r="X382" s="8">
         <v>13.606</v>
       </c>
-      <c r="Y382" s="9">
+      <c r="Y382" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z382" s="9">
+      <c r="Z382" s="8">
         <v>3.4</v>
       </c>
     </row>
@@ -29274,37 +29297,37 @@
         <f t="shared" si="5"/>
         <v>46234.100682870368</v>
       </c>
-      <c r="I383" s="9">
+      <c r="I383" s="8">
         <v>127.627296</v>
       </c>
-      <c r="J383" s="9">
+      <c r="J383" s="8">
         <v>1.4928509999999999</v>
       </c>
-      <c r="K383" s="9">
+      <c r="K383" s="8">
         <v>0.99299999999999999</v>
       </c>
-      <c r="L383" s="9">
+      <c r="L383" s="8">
         <v>1.056</v>
       </c>
-      <c r="M383" s="9">
+      <c r="M383" s="8">
         <v>181.27</v>
       </c>
-      <c r="N383" s="9">
+      <c r="N383" s="8">
         <v>8.2919999999999998</v>
       </c>
-      <c r="O383" s="9">
+      <c r="O383" s="8">
         <v>7.7709999999999999</v>
       </c>
-      <c r="P383" s="9">
+      <c r="P383" s="8">
         <v>32.770000000000003</v>
       </c>
-      <c r="Q383" s="9">
+      <c r="Q383" s="8">
         <v>-98.55</v>
       </c>
-      <c r="R383" s="9">
+      <c r="R383" s="8">
         <v>129.72</v>
       </c>
-      <c r="S383" s="9">
+      <c r="S383" s="8">
         <v>-64.680000000000007</v>
       </c>
       <c r="T383">
@@ -29313,19 +29336,19 @@
       <c r="U383">
         <v>317</v>
       </c>
-      <c r="V383" s="9">
+      <c r="V383" s="8">
         <v>-0.76</v>
       </c>
-      <c r="W383" s="9">
+      <c r="W383" s="8">
         <v>151.89400000000001</v>
       </c>
-      <c r="X383" s="9">
+      <c r="X383" s="8">
         <v>10.599</v>
       </c>
-      <c r="Y383" s="9">
+      <c r="Y383" s="8">
         <v>292.60000000000002</v>
       </c>
-      <c r="Z383" s="9">
+      <c r="Z383" s="8">
         <v>1.4</v>
       </c>
     </row>
@@ -29355,37 +29378,37 @@
         <f t="shared" si="5"/>
         <v>46203.079861111109</v>
       </c>
-      <c r="I384" s="9">
+      <c r="I384" s="8">
         <v>127.624756</v>
       </c>
-      <c r="J384" s="9">
+      <c r="J384" s="8">
         <v>1.4907319999999999</v>
       </c>
-      <c r="K384" s="9">
+      <c r="K384" s="8">
         <v>1.0469999999999999</v>
       </c>
-      <c r="L384" s="9">
+      <c r="L384" s="8">
         <v>1.1259999999999999</v>
       </c>
-      <c r="M384" s="9">
+      <c r="M384" s="8">
         <v>181.238</v>
       </c>
-      <c r="N384" s="9">
+      <c r="N384" s="8">
         <v>8.1389999999999993</v>
       </c>
-      <c r="O384" s="9">
+      <c r="O384" s="8">
         <v>7.6219999999999999</v>
       </c>
-      <c r="P384" s="9">
+      <c r="P384" s="8">
         <v>42.97</v>
       </c>
-      <c r="Q384" s="9">
+      <c r="Q384" s="8">
         <v>82.05</v>
       </c>
-      <c r="R384" s="9">
+      <c r="R384" s="8">
         <v>121.75</v>
       </c>
-      <c r="S384" s="9">
+      <c r="S384" s="8">
         <v>-61.35</v>
       </c>
       <c r="T384">
@@ -29394,19 +29417,19 @@
       <c r="U384">
         <v>1144</v>
       </c>
-      <c r="V384" s="9">
+      <c r="V384" s="8">
         <v>-0.74</v>
       </c>
-      <c r="W384" s="9">
+      <c r="W384" s="8">
         <v>85.536000000000001</v>
       </c>
-      <c r="X384" s="9">
+      <c r="X384" s="8">
         <v>11.574999999999999</v>
       </c>
-      <c r="Y384" s="9">
+      <c r="Y384" s="8">
         <v>293.5</v>
       </c>
-      <c r="Z384" s="9">
+      <c r="Z384" s="8">
         <v>1.8</v>
       </c>
     </row>
@@ -29436,37 +29459,37 @@
         <f t="shared" si="5"/>
         <v>46201.093738425923</v>
       </c>
-      <c r="I385" s="9">
+      <c r="I385" s="8">
         <v>127.63009599999999</v>
       </c>
-      <c r="J385" s="9">
+      <c r="J385" s="8">
         <v>1.4904850000000001</v>
       </c>
-      <c r="K385" s="9">
+      <c r="K385" s="8">
         <v>1.198</v>
       </c>
-      <c r="L385" s="9">
+      <c r="L385" s="8">
         <v>1.3520000000000001</v>
       </c>
-      <c r="M385" s="9">
+      <c r="M385" s="8">
         <v>181.23500000000001</v>
       </c>
-      <c r="N385" s="9">
+      <c r="N385" s="8">
         <v>8.5210000000000008</v>
       </c>
-      <c r="O385" s="9">
+      <c r="O385" s="8">
         <v>7.9080000000000004</v>
       </c>
-      <c r="P385" s="9">
+      <c r="P385" s="8">
         <v>1.26</v>
       </c>
-      <c r="Q385" s="9">
+      <c r="Q385" s="8">
         <v>86.8</v>
       </c>
-      <c r="R385" s="9">
+      <c r="R385" s="8">
         <v>126.17</v>
       </c>
-      <c r="S385" s="9">
+      <c r="S385" s="8">
         <v>-59.38</v>
       </c>
       <c r="T385">
@@ -29475,19 +29498,19 @@
       <c r="U385">
         <v>691</v>
       </c>
-      <c r="V385" s="9">
+      <c r="V385" s="8">
         <v>-0.71</v>
       </c>
-      <c r="W385" s="9">
+      <c r="W385" s="8">
         <v>125.247</v>
       </c>
-      <c r="X385" s="9">
+      <c r="X385" s="8">
         <v>15.871</v>
       </c>
-      <c r="Y385" s="9">
+      <c r="Y385" s="8">
         <v>293.39999999999998</v>
       </c>
-      <c r="Z385" s="9">
+      <c r="Z385" s="8">
         <v>2</v>
       </c>
     </row>
@@ -29517,37 +29540,37 @@
         <f t="shared" ref="H386:H398" si="6">(A386+2209125600)/86400</f>
         <v>46201.093738425923</v>
       </c>
-      <c r="I386" s="9">
+      <c r="I386" s="8">
         <v>127.628845</v>
       </c>
-      <c r="J386" s="9">
+      <c r="J386" s="8">
         <v>1.4992829999999999</v>
       </c>
-      <c r="K386" s="9">
+      <c r="K386" s="8">
         <v>0.93400000000000005</v>
       </c>
-      <c r="L386" s="9">
+      <c r="L386" s="8">
         <v>0.92600000000000005</v>
       </c>
-      <c r="M386" s="9">
+      <c r="M386" s="8">
         <v>181.23500000000001</v>
       </c>
-      <c r="N386" s="9">
+      <c r="N386" s="8">
         <v>8.4969999999999999</v>
       </c>
-      <c r="O386" s="9">
+      <c r="O386" s="8">
         <v>7.8940000000000001</v>
       </c>
-      <c r="P386" s="9">
+      <c r="P386" s="8">
         <v>1.26</v>
       </c>
-      <c r="Q386" s="9">
+      <c r="Q386" s="8">
         <v>90.87</v>
       </c>
-      <c r="R386" s="9">
+      <c r="R386" s="8">
         <v>126.17</v>
       </c>
-      <c r="S386" s="9">
+      <c r="S386" s="8">
         <v>-59.38</v>
       </c>
       <c r="T386">
@@ -29556,19 +29579,19 @@
       <c r="U386">
         <v>691</v>
       </c>
-      <c r="V386" s="9">
+      <c r="V386" s="8">
         <v>-0.79</v>
       </c>
-      <c r="W386" s="9">
+      <c r="W386" s="8">
         <v>125.19499999999999</v>
       </c>
-      <c r="X386" s="9">
+      <c r="X386" s="8">
         <v>7.82</v>
       </c>
-      <c r="Y386" s="9">
+      <c r="Y386" s="8">
         <v>293.39999999999998</v>
       </c>
-      <c r="Z386" s="9">
+      <c r="Z386" s="8">
         <v>2</v>
       </c>
     </row>
@@ -29598,37 +29621,37 @@
         <f t="shared" si="6"/>
         <v>46191.093738425923</v>
       </c>
-      <c r="I387" s="9">
+      <c r="I387" s="8">
         <v>127.630081</v>
       </c>
-      <c r="J387" s="9">
+      <c r="J387" s="8">
         <v>1.4925060000000001</v>
       </c>
-      <c r="K387" s="9">
+      <c r="K387" s="8">
         <v>1.242</v>
       </c>
-      <c r="L387" s="9">
+      <c r="L387" s="8">
         <v>1.3320000000000001</v>
       </c>
-      <c r="M387" s="9">
+      <c r="M387" s="8">
         <v>181.22</v>
       </c>
-      <c r="N387" s="9">
+      <c r="N387" s="8">
         <v>7.9930000000000003</v>
       </c>
-      <c r="O387" s="9">
+      <c r="O387" s="8">
         <v>7.4080000000000004</v>
       </c>
-      <c r="P387" s="9">
+      <c r="P387" s="8">
         <v>2.0099999999999998</v>
       </c>
-      <c r="Q387" s="9">
+      <c r="Q387" s="8">
         <v>-95.74</v>
       </c>
-      <c r="R387" s="9">
+      <c r="R387" s="8">
         <v>127.08</v>
       </c>
-      <c r="S387" s="9">
+      <c r="S387" s="8">
         <v>-59.02</v>
       </c>
       <c r="T387">
@@ -29637,19 +29660,19 @@
       <c r="U387">
         <v>655</v>
       </c>
-      <c r="V387" s="9">
+      <c r="V387" s="8">
         <v>-0.7</v>
       </c>
-      <c r="W387" s="9">
+      <c r="W387" s="8">
         <v>128.261</v>
       </c>
-      <c r="X387" s="9">
+      <c r="X387" s="8">
         <v>15.493</v>
       </c>
-      <c r="Y387" s="9">
+      <c r="Y387" s="8">
         <v>293.39999999999998</v>
       </c>
-      <c r="Z387" s="9">
+      <c r="Z387" s="8">
         <v>2</v>
       </c>
     </row>
@@ -29679,37 +29702,37 @@
         <f t="shared" si="6"/>
         <v>46186.371527777781</v>
       </c>
-      <c r="I388" s="9">
+      <c r="I388" s="8">
         <v>127.631378</v>
       </c>
-      <c r="J388" s="9">
+      <c r="J388" s="8">
         <v>1.4949539999999999</v>
       </c>
-      <c r="K388" s="9">
+      <c r="K388" s="8">
         <v>0.84399999999999997</v>
       </c>
-      <c r="L388" s="9">
+      <c r="L388" s="8">
         <v>0.86399999999999999</v>
       </c>
-      <c r="M388" s="9">
+      <c r="M388" s="8">
         <v>173.65799999999999</v>
       </c>
-      <c r="N388" s="9">
+      <c r="N388" s="8">
         <v>8.0649999999999995</v>
       </c>
-      <c r="O388" s="9">
+      <c r="O388" s="8">
         <v>7.4969999999999999</v>
       </c>
-      <c r="P388" s="9">
+      <c r="P388" s="8">
         <v>5.16</v>
       </c>
-      <c r="Q388" s="9">
+      <c r="Q388" s="8">
         <v>-84.22</v>
       </c>
-      <c r="R388" s="9">
+      <c r="R388" s="8">
         <v>123.19</v>
       </c>
-      <c r="S388" s="9">
+      <c r="S388" s="8">
         <v>60.43</v>
       </c>
       <c r="T388">
@@ -29718,19 +29741,19 @@
       <c r="U388">
         <v>734</v>
       </c>
-      <c r="V388" s="9">
+      <c r="V388" s="8">
         <v>-0.79</v>
       </c>
-      <c r="W388" s="9">
+      <c r="W388" s="8">
         <v>119.744</v>
       </c>
-      <c r="X388" s="9">
+      <c r="X388" s="8">
         <v>6.7859999999999996</v>
       </c>
-      <c r="Y388" s="9">
+      <c r="Y388" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z388" s="9">
+      <c r="Z388" s="8">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -29760,37 +29783,37 @@
         <f t="shared" si="6"/>
         <v>46176.097222222219</v>
       </c>
-      <c r="I389" s="9">
+      <c r="I389" s="8">
         <v>127.630745</v>
       </c>
-      <c r="J389" s="9">
+      <c r="J389" s="8">
         <v>1.4964280000000001</v>
       </c>
-      <c r="K389" s="9">
+      <c r="K389" s="8">
         <v>1.724</v>
       </c>
-      <c r="L389" s="9">
+      <c r="L389" s="8">
         <v>1.7250000000000001</v>
       </c>
-      <c r="M389" s="9">
+      <c r="M389" s="8">
         <v>181.411</v>
       </c>
-      <c r="N389" s="9">
+      <c r="N389" s="8">
         <v>8.3989999999999991</v>
       </c>
-      <c r="O389" s="9">
+      <c r="O389" s="8">
         <v>7.7270000000000003</v>
       </c>
-      <c r="P389" s="9">
+      <c r="P389" s="8">
         <v>6.47</v>
       </c>
-      <c r="Q389" s="9">
+      <c r="Q389" s="8">
         <v>-100.44</v>
       </c>
-      <c r="R389" s="9">
+      <c r="R389" s="8">
         <v>128.80000000000001</v>
       </c>
-      <c r="S389" s="9">
+      <c r="S389" s="8">
         <v>-59.46</v>
       </c>
       <c r="T389">
@@ -29799,19 +29822,19 @@
       <c r="U389">
         <v>605</v>
       </c>
-      <c r="V389" s="9">
+      <c r="V389" s="8">
         <v>-0.63</v>
       </c>
-      <c r="W389" s="9">
+      <c r="W389" s="8">
         <v>133.441</v>
       </c>
-      <c r="X389" s="9">
+      <c r="X389" s="8">
         <v>22.920999999999999</v>
       </c>
-      <c r="Y389" s="9">
+      <c r="Y389" s="8">
         <v>293.39999999999998</v>
       </c>
-      <c r="Z389" s="9">
+      <c r="Z389" s="8">
         <v>2</v>
       </c>
     </row>
@@ -29841,37 +29864,37 @@
         <f t="shared" si="6"/>
         <v>46171.097222222219</v>
       </c>
-      <c r="I390" s="9">
+      <c r="I390" s="8">
         <v>127.63215599999999</v>
       </c>
-      <c r="J390" s="9">
+      <c r="J390" s="8">
         <v>1.4930270000000001</v>
       </c>
-      <c r="K390" s="9">
+      <c r="K390" s="8">
         <v>0.79200000000000004</v>
       </c>
-      <c r="L390" s="9">
+      <c r="L390" s="8">
         <v>0.81399999999999995</v>
       </c>
-      <c r="M390" s="9">
+      <c r="M390" s="8">
         <v>181.40299999999999</v>
       </c>
-      <c r="N390" s="9">
+      <c r="N390" s="8">
         <v>7.673</v>
       </c>
-      <c r="O390" s="9">
+      <c r="O390" s="8">
         <v>7.1020000000000003</v>
       </c>
-      <c r="P390" s="9">
+      <c r="P390" s="8">
         <v>7.96</v>
       </c>
-      <c r="Q390" s="9">
+      <c r="Q390" s="8">
         <v>-95.4</v>
       </c>
-      <c r="R390" s="9">
+      <c r="R390" s="8">
         <v>129.49</v>
       </c>
-      <c r="S390" s="9">
+      <c r="S390" s="8">
         <v>-60.21</v>
       </c>
       <c r="T390">
@@ -29880,19 +29903,19 @@
       <c r="U390">
         <v>589</v>
       </c>
-      <c r="V390" s="9">
+      <c r="V390" s="8">
         <v>-0.79</v>
       </c>
-      <c r="W390" s="9">
+      <c r="W390" s="8">
         <v>135.417</v>
       </c>
-      <c r="X390" s="9">
+      <c r="X390" s="8">
         <v>5.5129999999999999</v>
       </c>
-      <c r="Y390" s="9">
+      <c r="Y390" s="8">
         <v>293.89999999999998</v>
       </c>
-      <c r="Z390" s="9">
+      <c r="Z390" s="8">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -29922,37 +29945,37 @@
         <f t="shared" si="6"/>
         <v>46131.104166666664</v>
       </c>
-      <c r="I391" s="9">
+      <c r="I391" s="8">
         <v>127.63157699999999</v>
       </c>
-      <c r="J391" s="9">
+      <c r="J391" s="8">
         <v>1.490175</v>
       </c>
-      <c r="K391" s="9">
+      <c r="K391" s="8">
         <v>1.0029999999999999</v>
       </c>
-      <c r="L391" s="9">
+      <c r="L391" s="8">
         <v>1</v>
       </c>
-      <c r="M391" s="9">
+      <c r="M391" s="8">
         <v>181.208</v>
       </c>
-      <c r="N391" s="9">
+      <c r="N391" s="8">
         <v>7.6509999999999998</v>
       </c>
-      <c r="O391" s="9">
+      <c r="O391" s="8">
         <v>7.1630000000000003</v>
       </c>
-      <c r="P391" s="9">
+      <c r="P391" s="8">
         <v>17.07</v>
       </c>
-      <c r="Q391" s="9">
+      <c r="Q391" s="8">
         <v>-97</v>
       </c>
-      <c r="R391" s="9">
+      <c r="R391" s="8">
         <v>133.96</v>
       </c>
-      <c r="S391" s="9">
+      <c r="S391" s="8">
         <v>-72.650000000000006</v>
       </c>
       <c r="T391">
@@ -29961,19 +29984,19 @@
       <c r="U391">
         <v>488</v>
       </c>
-      <c r="V391" s="9">
+      <c r="V391" s="8">
         <v>-0.75</v>
       </c>
-      <c r="W391" s="9">
+      <c r="W391" s="8">
         <v>148.803</v>
       </c>
-      <c r="X391" s="9">
+      <c r="X391" s="8">
         <v>9.1769999999999996</v>
       </c>
-      <c r="Y391" s="9">
+      <c r="Y391" s="8">
         <v>293.60000000000002</v>
       </c>
-      <c r="Z391" s="9">
+      <c r="Z391" s="8">
         <v>1.8</v>
       </c>
     </row>
@@ -30003,37 +30026,37 @@
         <f t="shared" si="6"/>
         <v>46131.104166666664</v>
       </c>
-      <c r="I392" s="9">
+      <c r="I392" s="8">
         <v>127.630623</v>
       </c>
-      <c r="J392" s="9">
+      <c r="J392" s="8">
         <v>1.4993460000000001</v>
       </c>
-      <c r="K392" s="9">
+      <c r="K392" s="8">
         <v>1.3560000000000001</v>
       </c>
-      <c r="L392" s="9">
+      <c r="L392" s="8">
         <v>1.4510000000000001</v>
       </c>
-      <c r="M392" s="9">
+      <c r="M392" s="8">
         <v>181.208</v>
       </c>
-      <c r="N392" s="9">
+      <c r="N392" s="8">
         <v>7.84</v>
       </c>
-      <c r="O392" s="9">
+      <c r="O392" s="8">
         <v>7.2949999999999999</v>
       </c>
-      <c r="P392" s="9">
+      <c r="P392" s="8">
         <v>17.07</v>
       </c>
-      <c r="Q392" s="9">
+      <c r="Q392" s="8">
         <v>-97.35</v>
       </c>
-      <c r="R392" s="9">
+      <c r="R392" s="8">
         <v>133.96</v>
       </c>
-      <c r="S392" s="9">
+      <c r="S392" s="8">
         <v>-72.64</v>
       </c>
       <c r="T392">
@@ -30042,19 +30065,19 @@
       <c r="U392">
         <v>488</v>
       </c>
-      <c r="V392" s="9">
+      <c r="V392" s="8">
         <v>-0.67</v>
       </c>
-      <c r="W392" s="9">
+      <c r="W392" s="8">
         <v>148.74</v>
       </c>
-      <c r="X392" s="9">
+      <c r="X392" s="8">
         <v>17.701000000000001</v>
       </c>
-      <c r="Y392" s="9">
+      <c r="Y392" s="8">
         <v>293.60000000000002</v>
       </c>
-      <c r="Z392" s="9">
+      <c r="Z392" s="8">
         <v>1.8</v>
       </c>
     </row>
@@ -30084,37 +30107,37 @@
         <f t="shared" si="6"/>
         <v>46116.364583333336</v>
       </c>
-      <c r="I393" s="9">
+      <c r="I393" s="8">
         <v>127.630768</v>
       </c>
-      <c r="J393" s="9">
+      <c r="J393" s="8">
         <v>1.4943690000000001</v>
       </c>
-      <c r="K393" s="9">
+      <c r="K393" s="8">
         <v>0.747</v>
       </c>
-      <c r="L393" s="9">
+      <c r="L393" s="8">
         <v>0.749</v>
       </c>
-      <c r="M393" s="9">
+      <c r="M393" s="8">
         <v>173.63</v>
       </c>
-      <c r="N393" s="9">
+      <c r="N393" s="8">
         <v>7.032</v>
       </c>
-      <c r="O393" s="9">
+      <c r="O393" s="8">
         <v>6.5730000000000004</v>
       </c>
-      <c r="P393" s="9">
+      <c r="P393" s="8">
         <v>4.93</v>
       </c>
-      <c r="Q393" s="9">
+      <c r="Q393" s="8">
         <v>99.06</v>
       </c>
-      <c r="R393" s="9">
+      <c r="R393" s="8">
         <v>130.97999999999999</v>
       </c>
-      <c r="S393" s="9">
+      <c r="S393" s="8">
         <v>80.66</v>
       </c>
       <c r="T393">
@@ -30123,19 +30146,19 @@
       <c r="U393">
         <v>622</v>
       </c>
-      <c r="V393" s="9">
+      <c r="V393" s="8">
         <v>-0.8</v>
       </c>
-      <c r="W393" s="9">
+      <c r="W393" s="8">
         <v>135.964</v>
       </c>
-      <c r="X393" s="9">
+      <c r="X393" s="8">
         <v>4.58</v>
       </c>
-      <c r="Y393" s="9">
+      <c r="Y393" s="8">
         <v>293.2</v>
       </c>
-      <c r="Z393" s="9">
+      <c r="Z393" s="8">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -30165,37 +30188,37 @@
         <f t="shared" si="6"/>
         <v>46111.368043981478</v>
       </c>
-      <c r="I394" s="9">
+      <c r="I394" s="8">
         <v>127.631844</v>
       </c>
-      <c r="J394" s="9">
+      <c r="J394" s="8">
         <v>1.498983</v>
       </c>
-      <c r="K394" s="9">
+      <c r="K394" s="8">
         <v>1.18</v>
       </c>
-      <c r="L394" s="9">
+      <c r="L394" s="8">
         <v>1.1990000000000001</v>
       </c>
-      <c r="M394" s="9">
+      <c r="M394" s="8">
         <v>173.62700000000001</v>
       </c>
-      <c r="N394" s="9">
+      <c r="N394" s="8">
         <v>8.3979999999999997</v>
       </c>
-      <c r="O394" s="9">
+      <c r="O394" s="8">
         <v>7.8390000000000004</v>
       </c>
-      <c r="P394" s="9">
+      <c r="P394" s="8">
         <v>11.12</v>
       </c>
-      <c r="Q394" s="9">
+      <c r="Q394" s="8">
         <v>-81.36</v>
       </c>
-      <c r="R394" s="9">
+      <c r="R394" s="8">
         <v>130.12</v>
       </c>
-      <c r="S394" s="9">
+      <c r="S394" s="8">
         <v>83.3</v>
       </c>
       <c r="T394">
@@ -30204,19 +30227,19 @@
       <c r="U394">
         <v>800</v>
       </c>
-      <c r="V394" s="9">
+      <c r="V394" s="8">
         <v>-0.73</v>
       </c>
-      <c r="W394" s="9">
+      <c r="W394" s="8">
         <v>119.892</v>
       </c>
-      <c r="X394" s="9">
+      <c r="X394" s="8">
         <v>13.101000000000001</v>
       </c>
-      <c r="Y394" s="9">
+      <c r="Y394" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z394" s="9">
+      <c r="Z394" s="8">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -30246,37 +30269,37 @@
         <f t="shared" si="6"/>
         <v>46111.104166666664</v>
       </c>
-      <c r="I395" s="9">
+      <c r="I395" s="8">
         <v>127.631485</v>
       </c>
-      <c r="J395" s="9">
+      <c r="J395" s="8">
         <v>1.498472</v>
       </c>
-      <c r="K395" s="9">
+      <c r="K395" s="8">
         <v>1.097</v>
       </c>
-      <c r="L395" s="9">
+      <c r="L395" s="8">
         <v>1.1459999999999999</v>
       </c>
-      <c r="M395" s="9">
+      <c r="M395" s="8">
         <v>181.11099999999999</v>
       </c>
-      <c r="N395" s="9">
+      <c r="N395" s="8">
         <v>8.3539999999999992</v>
       </c>
-      <c r="O395" s="9">
+      <c r="O395" s="8">
         <v>7.8109999999999999</v>
       </c>
-      <c r="P395" s="9">
+      <c r="P395" s="8">
         <v>20.45</v>
       </c>
-      <c r="Q395" s="9">
+      <c r="Q395" s="8">
         <v>-97.4</v>
       </c>
-      <c r="R395" s="9">
+      <c r="R395" s="8">
         <v>134.69999999999999</v>
       </c>
-      <c r="S395" s="9">
+      <c r="S395" s="8">
         <v>-83.02</v>
       </c>
       <c r="T395">
@@ -30285,19 +30308,19 @@
       <c r="U395">
         <v>451</v>
       </c>
-      <c r="V395" s="9">
+      <c r="V395" s="8">
         <v>-0.74</v>
       </c>
-      <c r="W395" s="9">
+      <c r="W395" s="8">
         <v>153.167</v>
       </c>
-      <c r="X395" s="9">
+      <c r="X395" s="8">
         <v>12.16</v>
       </c>
-      <c r="Y395" s="9">
+      <c r="Y395" s="8">
         <v>293</v>
       </c>
-      <c r="Z395" s="9">
+      <c r="Z395" s="8">
         <v>2.4</v>
       </c>
     </row>
@@ -30327,37 +30350,37 @@
         <f t="shared" si="6"/>
         <v>46106.104166666664</v>
       </c>
-      <c r="I396" s="9">
+      <c r="I396" s="8">
         <v>127.63001300000001</v>
       </c>
-      <c r="J396" s="9">
+      <c r="J396" s="8">
         <v>1.4964219999999999</v>
       </c>
-      <c r="K396" s="9">
+      <c r="K396" s="8">
         <v>1.746</v>
       </c>
-      <c r="L396" s="9">
+      <c r="L396" s="8">
         <v>1.891</v>
       </c>
-      <c r="M396" s="9">
+      <c r="M396" s="8">
         <v>181.10300000000001</v>
       </c>
-      <c r="N396" s="9">
+      <c r="N396" s="8">
         <v>8.5579999999999998</v>
       </c>
-      <c r="O396" s="9">
+      <c r="O396" s="8">
         <v>7.9589999999999996</v>
       </c>
-      <c r="P396" s="9">
+      <c r="P396" s="8">
         <v>21.08</v>
       </c>
-      <c r="Q396" s="9">
+      <c r="Q396" s="8">
         <v>-98.2</v>
       </c>
-      <c r="R396" s="9">
+      <c r="R396" s="8">
         <v>134.69999999999999</v>
       </c>
-      <c r="S396" s="9">
+      <c r="S396" s="8">
         <v>-85.75</v>
       </c>
       <c r="T396">
@@ -30366,19 +30389,19 @@
       <c r="U396">
         <v>444</v>
       </c>
-      <c r="V396" s="9">
+      <c r="V396" s="8">
         <v>-0.62</v>
       </c>
-      <c r="W396" s="9">
+      <c r="W396" s="8">
         <v>153.79</v>
       </c>
-      <c r="X396" s="9">
+      <c r="X396" s="8">
         <v>26.241</v>
       </c>
-      <c r="Y396" s="9">
+      <c r="Y396" s="8">
         <v>293</v>
       </c>
-      <c r="Z396" s="9">
+      <c r="Z396" s="8">
         <v>2.4</v>
       </c>
     </row>
@@ -30408,37 +30431,37 @@
         <f t="shared" si="6"/>
         <v>46066.111111111109</v>
       </c>
-      <c r="I397" s="9">
+      <c r="I397" s="8">
         <v>127.631477</v>
       </c>
-      <c r="J397" s="9">
+      <c r="J397" s="8">
         <v>1.4939629999999999</v>
       </c>
-      <c r="K397" s="9">
+      <c r="K397" s="8">
         <v>1.2929999999999999</v>
       </c>
-      <c r="L397" s="9">
+      <c r="L397" s="8">
         <v>1.3879999999999999</v>
       </c>
-      <c r="M397" s="9">
+      <c r="M397" s="8">
         <v>180.98</v>
       </c>
-      <c r="N397" s="9">
+      <c r="N397" s="8">
         <v>7.6950000000000003</v>
       </c>
-      <c r="O397" s="9">
+      <c r="O397" s="8">
         <v>7.0869999999999997</v>
       </c>
-      <c r="P397" s="9">
+      <c r="P397" s="8">
         <v>24.58</v>
       </c>
-      <c r="Q397" s="9">
+      <c r="Q397" s="8">
         <v>-97.06</v>
       </c>
-      <c r="R397" s="9">
+      <c r="R397" s="8">
         <v>133.1</v>
       </c>
-      <c r="S397" s="9">
+      <c r="S397" s="8">
         <v>-106.66</v>
       </c>
       <c r="T397">
@@ -30447,19 +30470,19 @@
       <c r="U397">
         <v>406</v>
       </c>
-      <c r="V397" s="9">
+      <c r="V397" s="8">
         <v>-0.67</v>
       </c>
-      <c r="W397" s="9">
+      <c r="W397" s="8">
         <v>156.98500000000001</v>
       </c>
-      <c r="X397" s="9">
+      <c r="X397" s="8">
         <v>16.677</v>
       </c>
-      <c r="Y397" s="9">
+      <c r="Y397" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z397" s="9">
+      <c r="Z397" s="8">
         <v>2.9</v>
       </c>
     </row>
@@ -30489,37 +30512,37 @@
         <f t="shared" si="6"/>
         <v>46031.111111111109</v>
       </c>
-      <c r="I398" s="9">
+      <c r="I398" s="8">
         <v>127.629761</v>
       </c>
-      <c r="J398" s="9">
+      <c r="J398" s="8">
         <v>1.49898</v>
       </c>
-      <c r="K398" s="9">
+      <c r="K398" s="8">
         <v>1.0189999999999999</v>
       </c>
-      <c r="L398" s="9">
+      <c r="L398" s="8">
         <v>1.147</v>
       </c>
-      <c r="M398" s="9">
+      <c r="M398" s="8">
         <v>180.333</v>
       </c>
-      <c r="N398" s="9">
+      <c r="N398" s="8">
         <v>8.1910000000000007</v>
       </c>
-      <c r="O398" s="9">
+      <c r="O398" s="8">
         <v>7.6459999999999999</v>
       </c>
-      <c r="P398" s="9">
+      <c r="P398" s="8">
         <v>24.47</v>
       </c>
-      <c r="Q398" s="9">
+      <c r="Q398" s="8">
         <v>-97.29</v>
       </c>
-      <c r="R398" s="9">
+      <c r="R398" s="8">
         <v>133.16</v>
       </c>
-      <c r="S398" s="9">
+      <c r="S398" s="8">
         <v>-118.96</v>
       </c>
       <c r="T398">
@@ -30528,19 +30551,19 @@
       <c r="U398">
         <v>407</v>
       </c>
-      <c r="V398" s="9">
+      <c r="V398" s="8">
         <v>-0.74</v>
       </c>
-      <c r="W398" s="9">
+      <c r="W398" s="8">
         <v>153.91200000000001</v>
       </c>
-      <c r="X398" s="9">
+      <c r="X398" s="8">
         <v>12.154999999999999</v>
       </c>
-      <c r="Y398" s="9">
+      <c r="Y398" s="8">
         <v>293.10000000000002</v>
       </c>
-      <c r="Z398" s="9">
+      <c r="Z398" s="8">
         <v>2</v>
       </c>
     </row>
@@ -42221,7 +42244,7 @@
       <c r="A372" t="s">
         <v>50</v>
       </c>
-      <c r="B372" s="9">
+      <c r="B372" s="8">
         <v>0.81599999999999995</v>
       </c>
       <c r="C372">
@@ -42243,13 +42266,13 @@
       <c r="H372" t="s">
         <v>50</v>
       </c>
-      <c r="I372" s="9">
+      <c r="I372" s="8">
         <v>1</v>
       </c>
-      <c r="J372" s="9">
+      <c r="J372" s="8">
         <v>0.81599999999999995</v>
       </c>
-      <c r="K372" s="9">
+      <c r="K372" s="8">
         <v>0.81599999999999995</v>
       </c>
     </row>
@@ -42257,7 +42280,7 @@
       <c r="A373" t="s">
         <v>51</v>
       </c>
-      <c r="B373" s="9">
+      <c r="B373" s="8">
         <v>0.89600000000000002</v>
       </c>
       <c r="C373">
@@ -42279,13 +42302,13 @@
       <c r="H373" t="s">
         <v>51</v>
       </c>
-      <c r="I373" s="9">
+      <c r="I373" s="8">
         <v>1</v>
       </c>
-      <c r="J373" s="9">
+      <c r="J373" s="8">
         <v>0.89600000000000002</v>
       </c>
-      <c r="K373" s="9">
+      <c r="K373" s="8">
         <v>0.89600000000000002</v>
       </c>
     </row>
@@ -42293,7 +42316,7 @@
       <c r="A374" t="s">
         <v>52</v>
       </c>
-      <c r="B374" s="9">
+      <c r="B374" s="8">
         <v>1.0409999999999999</v>
       </c>
       <c r="C374">
@@ -42315,13 +42338,13 @@
       <c r="H374" t="s">
         <v>52</v>
       </c>
-      <c r="I374" s="9">
+      <c r="I374" s="8">
         <v>1</v>
       </c>
-      <c r="J374" s="9">
+      <c r="J374" s="8">
         <v>1.0409999999999999</v>
       </c>
-      <c r="K374" s="9">
+      <c r="K374" s="8">
         <v>1.0409999999999999</v>
       </c>
     </row>
@@ -42329,7 +42352,7 @@
       <c r="A375" t="s">
         <v>53</v>
       </c>
-      <c r="B375" s="9">
+      <c r="B375" s="8">
         <v>1.57</v>
       </c>
       <c r="C375">
@@ -42351,13 +42374,13 @@
       <c r="H375" t="s">
         <v>53</v>
       </c>
-      <c r="I375" s="9">
+      <c r="I375" s="8">
         <v>2</v>
       </c>
-      <c r="J375" s="9">
+      <c r="J375" s="8">
         <v>1.57</v>
       </c>
-      <c r="K375" s="9">
+      <c r="K375" s="8">
         <v>2.4660000000000002</v>
       </c>
     </row>
@@ -42365,7 +42388,7 @@
       <c r="A376" t="s">
         <v>53</v>
       </c>
-      <c r="B376" s="9">
+      <c r="B376" s="8">
         <v>0.89600000000000002</v>
       </c>
       <c r="C376">
@@ -42387,13 +42410,13 @@
       <c r="H376" t="s">
         <v>54</v>
       </c>
-      <c r="I376" s="9">
+      <c r="I376" s="8">
         <v>1</v>
       </c>
-      <c r="J376" s="9">
+      <c r="J376" s="8">
         <v>1.5269999999999999</v>
       </c>
-      <c r="K376" s="9">
+      <c r="K376" s="8">
         <v>1.5269999999999999</v>
       </c>
     </row>
@@ -42401,7 +42424,7 @@
       <c r="A377" t="s">
         <v>54</v>
       </c>
-      <c r="B377" s="9">
+      <c r="B377" s="8">
         <v>1.5269999999999999</v>
       </c>
       <c r="C377">
@@ -42423,13 +42446,13 @@
       <c r="H377" t="s">
         <v>55</v>
       </c>
-      <c r="I377" s="9">
+      <c r="I377" s="8">
         <v>2</v>
       </c>
-      <c r="J377" s="9">
+      <c r="J377" s="8">
         <v>1.976</v>
       </c>
-      <c r="K377" s="9">
+      <c r="K377" s="8">
         <v>3.0760000000000001</v>
       </c>
     </row>
@@ -42437,7 +42460,7 @@
       <c r="A378" t="s">
         <v>55</v>
       </c>
-      <c r="B378" s="9">
+      <c r="B378" s="8">
         <v>1.1000000000000001</v>
       </c>
       <c r="C378">
@@ -42459,13 +42482,13 @@
       <c r="H378" t="s">
         <v>56</v>
       </c>
-      <c r="I378" s="9">
+      <c r="I378" s="8">
         <v>1</v>
       </c>
-      <c r="J378" s="9">
+      <c r="J378" s="8">
         <v>0.89600000000000002</v>
       </c>
-      <c r="K378" s="9">
+      <c r="K378" s="8">
         <v>0.89600000000000002</v>
       </c>
     </row>
@@ -42473,7 +42496,7 @@
       <c r="A379" t="s">
         <v>55</v>
       </c>
-      <c r="B379" s="9">
+      <c r="B379" s="8">
         <v>1.976</v>
       </c>
       <c r="C379">
@@ -42495,13 +42518,13 @@
       <c r="H379" t="s">
         <v>57</v>
       </c>
-      <c r="I379" s="9">
+      <c r="I379" s="8">
         <v>1</v>
       </c>
-      <c r="J379" s="9">
+      <c r="J379" s="8">
         <v>0.83</v>
       </c>
-      <c r="K379" s="9">
+      <c r="K379" s="8">
         <v>0.83</v>
       </c>
     </row>
@@ -42509,7 +42532,7 @@
       <c r="A380" t="s">
         <v>56</v>
       </c>
-      <c r="B380" s="9">
+      <c r="B380" s="8">
         <v>0.89600000000000002</v>
       </c>
       <c r="C380">
@@ -42531,13 +42554,13 @@
       <c r="H380" t="s">
         <v>58</v>
       </c>
-      <c r="I380" s="9">
+      <c r="I380" s="8">
         <v>1</v>
       </c>
-      <c r="J380" s="9">
+      <c r="J380" s="8">
         <v>1.1479999999999999</v>
       </c>
-      <c r="K380" s="9">
+      <c r="K380" s="8">
         <v>1.1479999999999999</v>
       </c>
     </row>
@@ -42545,7 +42568,7 @@
       <c r="A381" t="s">
         <v>57</v>
       </c>
-      <c r="B381" s="9">
+      <c r="B381" s="8">
         <v>0.83</v>
       </c>
       <c r="C381">
@@ -42567,13 +42590,13 @@
       <c r="H381" t="s">
         <v>59</v>
       </c>
-      <c r="I381" s="9">
+      <c r="I381" s="8">
         <v>1</v>
       </c>
-      <c r="J381" s="9">
+      <c r="J381" s="8">
         <v>0.99299999999999999</v>
       </c>
-      <c r="K381" s="9">
+      <c r="K381" s="8">
         <v>0.99299999999999999</v>
       </c>
     </row>
@@ -42581,7 +42604,7 @@
       <c r="A382" t="s">
         <v>58</v>
       </c>
-      <c r="B382" s="9">
+      <c r="B382" s="8">
         <v>1.1479999999999999</v>
       </c>
       <c r="C382">
@@ -42603,13 +42626,13 @@
       <c r="H382" t="s">
         <v>60</v>
       </c>
-      <c r="I382" s="9">
+      <c r="I382" s="8">
         <v>1</v>
       </c>
-      <c r="J382" s="9">
+      <c r="J382" s="8">
         <v>1.0469999999999999</v>
       </c>
-      <c r="K382" s="9">
+      <c r="K382" s="8">
         <v>1.0469999999999999</v>
       </c>
     </row>
@@ -42617,7 +42640,7 @@
       <c r="A383" t="s">
         <v>59</v>
       </c>
-      <c r="B383" s="9">
+      <c r="B383" s="8">
         <v>0.99299999999999999</v>
       </c>
       <c r="C383">
@@ -42639,13 +42662,13 @@
       <c r="H383" t="s">
         <v>61</v>
       </c>
-      <c r="I383" s="9">
+      <c r="I383" s="8">
         <v>2</v>
       </c>
-      <c r="J383" s="9">
+      <c r="J383" s="8">
         <v>1.198</v>
       </c>
-      <c r="K383" s="9">
+      <c r="K383" s="8">
         <v>2.1320000000000001</v>
       </c>
     </row>
@@ -42653,7 +42676,7 @@
       <c r="A384" t="s">
         <v>60</v>
       </c>
-      <c r="B384" s="9">
+      <c r="B384" s="8">
         <v>1.0469999999999999</v>
       </c>
       <c r="C384">
@@ -42675,13 +42698,13 @@
       <c r="H384" t="s">
         <v>62</v>
       </c>
-      <c r="I384" s="9">
+      <c r="I384" s="8">
         <v>1</v>
       </c>
-      <c r="J384" s="9">
+      <c r="J384" s="8">
         <v>1.242</v>
       </c>
-      <c r="K384" s="9">
+      <c r="K384" s="8">
         <v>1.242</v>
       </c>
     </row>
@@ -42689,7 +42712,7 @@
       <c r="A385" t="s">
         <v>61</v>
       </c>
-      <c r="B385" s="9">
+      <c r="B385" s="8">
         <v>1.198</v>
       </c>
       <c r="C385">
@@ -42711,13 +42734,13 @@
       <c r="H385" t="s">
         <v>63</v>
       </c>
-      <c r="I385" s="9">
+      <c r="I385" s="8">
         <v>1</v>
       </c>
-      <c r="J385" s="9">
+      <c r="J385" s="8">
         <v>0.84399999999999997</v>
       </c>
-      <c r="K385" s="9">
+      <c r="K385" s="8">
         <v>0.84399999999999997</v>
       </c>
     </row>
@@ -42725,7 +42748,7 @@
       <c r="A386" t="s">
         <v>61</v>
       </c>
-      <c r="B386" s="9">
+      <c r="B386" s="8">
         <v>0.93400000000000005</v>
       </c>
       <c r="C386">
@@ -42747,13 +42770,13 @@
       <c r="H386" t="s">
         <v>64</v>
       </c>
-      <c r="I386" s="9">
+      <c r="I386" s="8">
         <v>1</v>
       </c>
-      <c r="J386" s="9">
+      <c r="J386" s="8">
         <v>1.724</v>
       </c>
-      <c r="K386" s="9">
+      <c r="K386" s="8">
         <v>1.724</v>
       </c>
     </row>
@@ -42761,7 +42784,7 @@
       <c r="A387" t="s">
         <v>62</v>
       </c>
-      <c r="B387" s="9">
+      <c r="B387" s="8">
         <v>1.242</v>
       </c>
       <c r="C387">
@@ -42783,13 +42806,13 @@
       <c r="H387" t="s">
         <v>65</v>
       </c>
-      <c r="I387" s="9">
+      <c r="I387" s="8">
         <v>1</v>
       </c>
-      <c r="J387" s="9">
+      <c r="J387" s="8">
         <v>0.79200000000000004</v>
       </c>
-      <c r="K387" s="9">
+      <c r="K387" s="8">
         <v>0.79200000000000004</v>
       </c>
     </row>
@@ -42797,7 +42820,7 @@
       <c r="A388" t="s">
         <v>63</v>
       </c>
-      <c r="B388" s="9">
+      <c r="B388" s="8">
         <v>0.84399999999999997</v>
       </c>
       <c r="C388">
@@ -42819,13 +42842,13 @@
       <c r="H388" t="s">
         <v>66</v>
       </c>
-      <c r="I388" s="9">
+      <c r="I388" s="8">
         <v>2</v>
       </c>
-      <c r="J388" s="9">
+      <c r="J388" s="8">
         <v>1.3560000000000001</v>
       </c>
-      <c r="K388" s="9">
+      <c r="K388" s="8">
         <v>2.359</v>
       </c>
     </row>
@@ -42833,7 +42856,7 @@
       <c r="A389" t="s">
         <v>64</v>
       </c>
-      <c r="B389" s="9">
+      <c r="B389" s="8">
         <v>1.724</v>
       </c>
       <c r="C389">
@@ -42855,13 +42878,13 @@
       <c r="H389" t="s">
         <v>67</v>
       </c>
-      <c r="I389" s="9">
+      <c r="I389" s="8">
         <v>1</v>
       </c>
-      <c r="J389" s="9">
+      <c r="J389" s="8">
         <v>0.747</v>
       </c>
-      <c r="K389" s="9">
+      <c r="K389" s="8">
         <v>0.747</v>
       </c>
     </row>
@@ -42869,7 +42892,7 @@
       <c r="A390" t="s">
         <v>65</v>
       </c>
-      <c r="B390" s="9">
+      <c r="B390" s="8">
         <v>0.79200000000000004</v>
       </c>
       <c r="C390">
@@ -42891,13 +42914,13 @@
       <c r="H390" t="s">
         <v>68</v>
       </c>
-      <c r="I390" s="9">
+      <c r="I390" s="8">
         <v>1</v>
       </c>
-      <c r="J390" s="9">
+      <c r="J390" s="8">
         <v>1.18</v>
       </c>
-      <c r="K390" s="9">
+      <c r="K390" s="8">
         <v>1.18</v>
       </c>
     </row>
@@ -42905,7 +42928,7 @@
       <c r="A391" t="s">
         <v>66</v>
       </c>
-      <c r="B391" s="9">
+      <c r="B391" s="8">
         <v>1.0029999999999999</v>
       </c>
       <c r="C391">
@@ -42927,13 +42950,13 @@
       <c r="H391" t="s">
         <v>69</v>
       </c>
-      <c r="I391" s="9">
+      <c r="I391" s="8">
         <v>1</v>
       </c>
-      <c r="J391" s="9">
+      <c r="J391" s="8">
         <v>1.097</v>
       </c>
-      <c r="K391" s="9">
+      <c r="K391" s="8">
         <v>1.097</v>
       </c>
     </row>
@@ -42941,7 +42964,7 @@
       <c r="A392" t="s">
         <v>66</v>
       </c>
-      <c r="B392" s="9">
+      <c r="B392" s="8">
         <v>1.3560000000000001</v>
       </c>
       <c r="C392">
@@ -42963,13 +42986,13 @@
       <c r="H392" t="s">
         <v>70</v>
       </c>
-      <c r="I392" s="9">
+      <c r="I392" s="8">
         <v>1</v>
       </c>
-      <c r="J392" s="9">
+      <c r="J392" s="8">
         <v>1.746</v>
       </c>
-      <c r="K392" s="9">
+      <c r="K392" s="8">
         <v>1.746</v>
       </c>
     </row>
@@ -42977,7 +43000,7 @@
       <c r="A393" t="s">
         <v>67</v>
       </c>
-      <c r="B393" s="9">
+      <c r="B393" s="8">
         <v>0.747</v>
       </c>
       <c r="C393">
@@ -42999,13 +43022,13 @@
       <c r="H393" t="s">
         <v>71</v>
       </c>
-      <c r="I393" s="9">
+      <c r="I393" s="8">
         <v>1</v>
       </c>
-      <c r="J393" s="9">
+      <c r="J393" s="8">
         <v>1.2929999999999999</v>
       </c>
-      <c r="K393" s="9">
+      <c r="K393" s="8">
         <v>1.2929999999999999</v>
       </c>
     </row>
@@ -43013,7 +43036,7 @@
       <c r="A394" t="s">
         <v>68</v>
       </c>
-      <c r="B394" s="9">
+      <c r="B394" s="8">
         <v>1.18</v>
       </c>
       <c r="C394">
@@ -43035,13 +43058,13 @@
       <c r="H394" t="s">
         <v>72</v>
       </c>
-      <c r="I394" s="9">
+      <c r="I394" s="8">
         <v>1</v>
       </c>
-      <c r="J394" s="9">
+      <c r="J394" s="8">
         <v>1.0189999999999999</v>
       </c>
-      <c r="K394" s="9">
+      <c r="K394" s="8">
         <v>1.0189999999999999</v>
       </c>
     </row>
@@ -43049,7 +43072,7 @@
       <c r="A395" t="s">
         <v>69</v>
       </c>
-      <c r="B395" s="9">
+      <c r="B395" s="8">
         <v>1.097</v>
       </c>
       <c r="C395">
@@ -43073,7 +43096,7 @@
       <c r="A396" t="s">
         <v>70</v>
       </c>
-      <c r="B396" s="9">
+      <c r="B396" s="8">
         <v>1.746</v>
       </c>
       <c r="C396">
@@ -43097,7 +43120,7 @@
       <c r="A397" t="s">
         <v>71</v>
       </c>
-      <c r="B397" s="9">
+      <c r="B397" s="8">
         <v>1.2929999999999999</v>
       </c>
       <c r="C397">
@@ -43121,7 +43144,7 @@
       <c r="A398" t="s">
         <v>72</v>
       </c>
-      <c r="B398" s="9">
+      <c r="B398" s="8">
         <v>1.0189999999999999</v>
       </c>
       <c r="C398">
@@ -43163,40 +43186,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="14" t="s">
         <v>38</v>
       </c>
       <c r="N1" t="s">
@@ -43220,25 +43243,26 @@
       <c r="T1" t="s">
         <v>38</v>
       </c>
-      <c r="W1" t="s">
+      <c r="V1" s="15"/>
+      <c r="W1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="15" t="s">
         <v>38</v>
       </c>
     </row>
@@ -43249,7 +43273,7 @@
       <c r="B2">
         <v>0.60099999999999998</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>(0.45*B2)-0.127</f>
         <v>0.14345000000000002</v>
       </c>
@@ -43349,7 +43373,7 @@
       <c r="B3">
         <v>0.54900000000000004</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f t="shared" ref="C3" si="5">(0.45*B3)-0.127</f>
         <v>0.12005000000000002</v>
       </c>
@@ -43459,7 +43483,7 @@
       <c r="B4">
         <v>3.734</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f t="shared" ref="C4:C67" si="11">(0.45*B4)-0.127</f>
         <v>1.5533000000000001</v>
       </c>
@@ -43569,7 +43593,7 @@
       <c r="B5">
         <v>5.6559999999999997</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f t="shared" si="11"/>
         <v>2.4181999999999997</v>
       </c>
@@ -43679,7 +43703,7 @@
       <c r="B6">
         <v>7.0689999999999991</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f t="shared" si="11"/>
         <v>3.0540499999999993</v>
       </c>
@@ -43789,7 +43813,7 @@
       <c r="B7">
         <v>10.516</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f t="shared" si="11"/>
         <v>4.6052</v>
       </c>
@@ -43899,7 +43923,7 @@
       <c r="B8">
         <v>3.4660000000000002</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f t="shared" si="11"/>
         <v>1.4327000000000001</v>
       </c>
@@ -44009,7 +44033,7 @@
       <c r="B9">
         <v>4.5369999999999999</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f t="shared" si="11"/>
         <v>1.9146500000000002</v>
       </c>
@@ -44119,7 +44143,7 @@
       <c r="B10">
         <v>2.7629999999999999</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f t="shared" si="11"/>
         <v>1.11635</v>
       </c>
@@ -44229,7 +44253,7 @@
       <c r="B11">
         <v>3.4870000000000001</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f t="shared" si="11"/>
         <v>1.44215</v>
       </c>
@@ -44339,7 +44363,7 @@
       <c r="B12">
         <v>1.65</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f t="shared" si="11"/>
         <v>0.61549999999999994</v>
       </c>
@@ -44449,7 +44473,7 @@
       <c r="B13">
         <v>3.2549999999999999</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f t="shared" si="11"/>
         <v>1.33775</v>
       </c>
@@ -44559,7 +44583,7 @@
       <c r="B14">
         <v>3.2650000000000001</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f t="shared" si="11"/>
         <v>1.3422500000000002</v>
       </c>
@@ -44669,7 +44693,7 @@
       <c r="B15">
         <v>3.0510000000000002</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f t="shared" si="11"/>
         <v>1.2459500000000001</v>
       </c>
@@ -44779,7 +44803,7 @@
       <c r="B16">
         <v>2.3839999999999999</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f t="shared" si="11"/>
         <v>0.94579999999999997</v>
       </c>
@@ -44889,7 +44913,7 @@
       <c r="B17">
         <v>0.83299999999999996</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f t="shared" si="11"/>
         <v>0.24785000000000001</v>
       </c>
@@ -44999,7 +45023,7 @@
       <c r="B18">
         <v>0.98699999999999999</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f t="shared" si="11"/>
         <v>0.31714999999999999</v>
       </c>
@@ -45109,7 +45133,7 @@
       <c r="B19">
         <v>1.4</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f t="shared" si="11"/>
         <v>0.503</v>
       </c>
@@ -45219,7 +45243,7 @@
       <c r="B20">
         <v>4.63</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <f t="shared" si="11"/>
         <v>1.9564999999999999</v>
       </c>
@@ -45329,7 +45353,7 @@
       <c r="B21">
         <v>1.8639999999999999</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <f t="shared" si="11"/>
         <v>0.71179999999999999</v>
       </c>
@@ -45439,7 +45463,7 @@
       <c r="B22">
         <v>1.4169999999999998</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <f t="shared" si="11"/>
         <v>0.51064999999999994</v>
       </c>
@@ -45549,7 +45573,7 @@
       <c r="B23">
         <v>3.262</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <f t="shared" si="11"/>
         <v>1.3409</v>
       </c>
@@ -45659,7 +45683,7 @@
       <c r="B24">
         <v>1.7669999999999999</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <f t="shared" si="11"/>
         <v>0.66815000000000002</v>
       </c>
@@ -45769,7 +45793,7 @@
       <c r="B25">
         <v>0.97099999999999997</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="2">
         <f t="shared" si="11"/>
         <v>0.30995</v>
       </c>
@@ -45879,7 +45903,7 @@
       <c r="B26">
         <v>3.63</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <f t="shared" si="11"/>
         <v>1.5065</v>
       </c>
@@ -45989,7 +46013,7 @@
       <c r="B27">
         <v>4.0299999999999994</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="2">
         <f t="shared" si="11"/>
         <v>1.6864999999999997</v>
       </c>
@@ -46099,7 +46123,7 @@
       <c r="B28">
         <v>5.6340000000000003</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="2">
         <f t="shared" si="11"/>
         <v>2.4083000000000006</v>
       </c>
@@ -46209,7 +46233,7 @@
       <c r="B29">
         <v>3.59</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="2">
         <f t="shared" si="11"/>
         <v>1.4884999999999999</v>
       </c>
@@ -46319,7 +46343,7 @@
       <c r="B30">
         <v>1.869</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="2">
         <f t="shared" si="11"/>
         <v>0.71404999999999996</v>
       </c>
@@ -46429,7 +46453,7 @@
       <c r="B31">
         <v>4.8330000000000002</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="2">
         <f t="shared" si="11"/>
         <v>2.0478500000000004</v>
       </c>
@@ -46539,7 +46563,7 @@
       <c r="B32">
         <v>5.3959999999999999</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <f t="shared" si="11"/>
         <v>2.3011999999999997</v>
       </c>
@@ -46649,7 +46673,7 @@
       <c r="B33">
         <v>4.1929999999999996</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="2">
         <f t="shared" si="11"/>
         <v>1.7598499999999999</v>
       </c>
@@ -46759,7 +46783,7 @@
       <c r="B34">
         <v>5.5830000000000002</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="2">
         <f t="shared" si="11"/>
         <v>2.3853499999999999</v>
       </c>
@@ -46869,7 +46893,7 @@
       <c r="B35">
         <v>6.7439999999999998</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="2">
         <f t="shared" si="11"/>
         <v>2.9077999999999999</v>
       </c>
@@ -46979,7 +47003,7 @@
       <c r="B36">
         <v>1.387</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="2">
         <f t="shared" si="11"/>
         <v>0.49714999999999998</v>
       </c>
@@ -47089,7 +47113,7 @@
       <c r="B37">
         <v>1.5229999999999999</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="2">
         <f t="shared" si="11"/>
         <v>0.55835000000000001</v>
       </c>
@@ -47199,7 +47223,7 @@
       <c r="B38">
         <v>2.3179999999999996</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="2">
         <f t="shared" si="11"/>
         <v>0.91609999999999991</v>
       </c>
@@ -47309,7 +47333,7 @@
       <c r="B39">
         <v>0.72599999999999998</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="2">
         <f t="shared" si="11"/>
         <v>0.19969999999999999</v>
       </c>
@@ -47419,7 +47443,7 @@
       <c r="B40">
         <v>3.8420000000000001</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="2">
         <f t="shared" si="11"/>
         <v>1.6019000000000001</v>
       </c>
@@ -47467,7 +47491,7 @@
       <c r="B41">
         <v>6.9570000000000007</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="2">
         <f t="shared" si="11"/>
         <v>3.0036500000000004</v>
       </c>
@@ -47515,7 +47539,7 @@
       <c r="B42">
         <v>2.2170000000000001</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="2">
         <f t="shared" si="11"/>
         <v>0.87065000000000003</v>
       </c>
@@ -47563,7 +47587,7 @@
       <c r="B43">
         <v>5.8570000000000002</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="2">
         <f t="shared" si="11"/>
         <v>2.5086500000000003</v>
       </c>
@@ -47611,7 +47635,7 @@
       <c r="B44">
         <v>1.9890000000000001</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="2">
         <f t="shared" si="11"/>
         <v>0.76805000000000001</v>
       </c>
@@ -47659,7 +47683,7 @@
       <c r="B45">
         <v>3.2239999999999998</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="2">
         <f t="shared" si="11"/>
         <v>1.3237999999999999</v>
       </c>
@@ -47723,7 +47747,7 @@
       <c r="B46">
         <v>1.744</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="2">
         <f t="shared" si="11"/>
         <v>0.65780000000000005</v>
       </c>
@@ -47787,7 +47811,7 @@
       <c r="B47">
         <v>1.738</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="2">
         <f t="shared" si="11"/>
         <v>0.65510000000000002</v>
       </c>
@@ -47851,7 +47875,7 @@
       <c r="B48">
         <v>1.0720000000000001</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="2">
         <f t="shared" si="11"/>
         <v>0.35540000000000005</v>
       </c>
@@ -47899,7 +47923,7 @@
       <c r="B49">
         <v>2.84</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="2">
         <f t="shared" si="11"/>
         <v>1.151</v>
       </c>
@@ -47947,7 +47971,7 @@
       <c r="B50">
         <v>1.9490000000000001</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="2">
         <f t="shared" si="11"/>
         <v>0.75004999999999999</v>
       </c>
@@ -47995,7 +48019,7 @@
       <c r="B51">
         <v>1.387</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="2">
         <f t="shared" si="11"/>
         <v>0.49714999999999998</v>
       </c>
@@ -48043,7 +48067,7 @@
       <c r="B52">
         <v>1.694</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="2">
         <f t="shared" si="11"/>
         <v>0.63529999999999998</v>
       </c>
@@ -48091,7 +48115,7 @@
       <c r="B53">
         <v>0.98099999999999998</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="2">
         <f t="shared" si="11"/>
         <v>0.31445000000000001</v>
       </c>
@@ -48139,7 +48163,7 @@
       <c r="B54">
         <v>3.4510000000000001</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="2">
         <f t="shared" si="11"/>
         <v>1.4259500000000001</v>
       </c>
@@ -48187,7 +48211,7 @@
       <c r="B55">
         <v>1.675</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="2">
         <f t="shared" si="11"/>
         <v>0.62675000000000003</v>
       </c>
@@ -48235,7 +48259,7 @@
       <c r="B56">
         <v>7.1489999999999991</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="2">
         <f t="shared" si="11"/>
         <v>3.0900499999999997</v>
       </c>
@@ -48283,7 +48307,7 @@
       <c r="B57">
         <v>3.0059999999999998</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="2">
         <f t="shared" si="11"/>
         <v>1.2257</v>
       </c>
@@ -48331,7 +48355,7 @@
       <c r="B58">
         <v>1.113</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="2">
         <f t="shared" si="11"/>
         <v>0.37385000000000002</v>
       </c>
@@ -48379,7 +48403,7 @@
       <c r="B59">
         <v>2.0030000000000001</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="2">
         <f t="shared" si="11"/>
         <v>0.77435000000000009</v>
       </c>
@@ -48427,7 +48451,7 @@
       <c r="B60">
         <v>1.05</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="2">
         <f t="shared" si="11"/>
         <v>0.34550000000000003</v>
       </c>
@@ -48475,7 +48499,7 @@
       <c r="B61">
         <v>2.8639999999999999</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="2">
         <f t="shared" si="11"/>
         <v>1.1617999999999999</v>
       </c>
@@ -48523,7 +48547,7 @@
       <c r="B62">
         <v>1.0720000000000001</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="2">
         <f t="shared" si="11"/>
         <v>0.35540000000000005</v>
       </c>
@@ -48571,7 +48595,7 @@
       <c r="B63">
         <v>3.0939999999999999</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="2">
         <f t="shared" si="11"/>
         <v>1.2652999999999999</v>
       </c>
@@ -48619,7 +48643,7 @@
       <c r="B64">
         <v>0.97099999999999997</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="2">
         <f t="shared" si="11"/>
         <v>0.30995</v>
       </c>
@@ -48667,7 +48691,7 @@
       <c r="B65">
         <v>4.7569999999999997</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="2">
         <f t="shared" si="11"/>
         <v>2.0136500000000002</v>
       </c>
@@ -48715,7 +48739,7 @@
       <c r="B66">
         <v>2.76</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="2">
         <f t="shared" si="11"/>
         <v>1.115</v>
       </c>
@@ -48763,7 +48787,7 @@
       <c r="B67">
         <v>2.3929999999999998</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="2">
         <f t="shared" si="11"/>
         <v>0.94984999999999986</v>
       </c>
@@ -48811,7 +48835,7 @@
       <c r="B68">
         <v>1.3149999999999999</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="2">
         <f t="shared" ref="C68:C131" si="37">(0.45*B68)-0.127</f>
         <v>0.46475</v>
       </c>
@@ -48859,7 +48883,7 @@
       <c r="B69">
         <v>4.4329999999999998</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="2">
         <f t="shared" si="37"/>
         <v>1.86785</v>
       </c>
@@ -48907,7 +48931,7 @@
       <c r="B70">
         <v>2.0469999999999997</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="2">
         <f t="shared" si="37"/>
         <v>0.79414999999999991</v>
       </c>
@@ -48955,7 +48979,7 @@
       <c r="B71">
         <v>3.4829999999999997</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="2">
         <f t="shared" si="37"/>
         <v>1.4403499999999998</v>
       </c>
@@ -49003,7 +49027,7 @@
       <c r="B72">
         <v>2.085</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="2">
         <f t="shared" si="37"/>
         <v>0.81125000000000003</v>
       </c>
@@ -49051,7 +49075,7 @@
       <c r="B73">
         <v>3.198</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="2">
         <f t="shared" si="37"/>
         <v>1.3121</v>
       </c>
@@ -49099,7 +49123,7 @@
       <c r="B74">
         <v>3.5440000000000005</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="2">
         <f t="shared" si="37"/>
         <v>1.4678000000000002</v>
       </c>
@@ -49147,7 +49171,7 @@
       <c r="B75">
         <v>0.96499999999999997</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="2">
         <f t="shared" si="37"/>
         <v>0.30724999999999997</v>
       </c>
@@ -49195,7 +49219,7 @@
       <c r="B76">
         <v>2.593</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="2">
         <f t="shared" si="37"/>
         <v>1.0398499999999999</v>
       </c>
@@ -49243,7 +49267,7 @@
       <c r="B77">
         <v>0.35399999999999998</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77" s="2">
         <f t="shared" si="37"/>
         <v>3.2299999999999995E-2</v>
       </c>
@@ -49291,7 +49315,7 @@
       <c r="B78">
         <v>7.5429999999999993</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78" s="2">
         <f t="shared" si="37"/>
         <v>3.2673499999999995</v>
       </c>
@@ -49339,7 +49363,7 @@
       <c r="B79">
         <v>2.46</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79" s="2">
         <f t="shared" si="37"/>
         <v>0.98</v>
       </c>
@@ -49387,7 +49411,7 @@
       <c r="B80">
         <v>2.4169999999999998</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80" s="2">
         <f t="shared" si="37"/>
         <v>0.96065</v>
       </c>
@@ -49435,7 +49459,7 @@
       <c r="B81">
         <v>2.9089999999999998</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81" s="2">
         <f t="shared" si="37"/>
         <v>1.18205</v>
       </c>
@@ -49483,7 +49507,7 @@
       <c r="B82">
         <v>2.1789999999999998</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82" s="2">
         <f t="shared" si="37"/>
         <v>0.85354999999999992</v>
       </c>
@@ -49531,7 +49555,7 @@
       <c r="B83">
         <v>1.5209999999999999</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C83" s="2">
         <f t="shared" si="37"/>
         <v>0.55745</v>
       </c>
@@ -49579,7 +49603,7 @@
       <c r="B84">
         <v>4.4289999999999994</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C84" s="2">
         <f t="shared" si="37"/>
         <v>1.8660499999999998</v>
       </c>
@@ -49627,7 +49651,7 @@
       <c r="B85">
         <v>0.82299999999999995</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85" s="2">
         <f t="shared" si="37"/>
         <v>0.24335000000000001</v>
       </c>
@@ -49675,7 +49699,7 @@
       <c r="B86">
         <v>0.38600000000000001</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86" s="2">
         <f t="shared" si="37"/>
         <v>4.6700000000000019E-2</v>
       </c>
@@ -49723,7 +49747,7 @@
       <c r="B87">
         <v>1.57</v>
       </c>
-      <c r="C87" s="3">
+      <c r="C87" s="2">
         <f t="shared" si="37"/>
         <v>0.57950000000000002</v>
       </c>
@@ -49771,7 +49795,7 @@
       <c r="B88">
         <v>1.498</v>
       </c>
-      <c r="C88" s="3">
+      <c r="C88" s="2">
         <f t="shared" si="37"/>
         <v>0.54710000000000003</v>
       </c>
@@ -49819,7 +49843,7 @@
       <c r="B89">
         <v>3.3820000000000001</v>
       </c>
-      <c r="C89" s="3">
+      <c r="C89" s="2">
         <f t="shared" si="37"/>
         <v>1.3949</v>
       </c>
@@ -49867,7 +49891,7 @@
       <c r="B90">
         <v>3.673</v>
       </c>
-      <c r="C90" s="3">
+      <c r="C90" s="2">
         <f t="shared" si="37"/>
         <v>1.5258500000000002</v>
       </c>
@@ -49915,7 +49939,7 @@
       <c r="B91">
         <v>0.72299999999999998</v>
       </c>
-      <c r="C91" s="3">
+      <c r="C91" s="2">
         <f t="shared" si="37"/>
         <v>0.19834999999999997</v>
       </c>
@@ -49963,7 +49987,7 @@
       <c r="B92">
         <v>3.181</v>
       </c>
-      <c r="C92" s="3">
+      <c r="C92" s="2">
         <f t="shared" si="37"/>
         <v>1.3044500000000001</v>
       </c>
@@ -50011,7 +50035,7 @@
       <c r="B93">
         <v>0.54300000000000004</v>
       </c>
-      <c r="C93" s="3">
+      <c r="C93" s="2">
         <f t="shared" si="37"/>
         <v>0.11735000000000001</v>
       </c>
@@ -50059,7 +50083,7 @@
       <c r="B94">
         <v>1.0089999999999999</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C94" s="2">
         <f t="shared" si="37"/>
         <v>0.32704999999999995</v>
       </c>
@@ -50107,7 +50131,7 @@
       <c r="B95">
         <v>1.524</v>
       </c>
-      <c r="C95" s="3">
+      <c r="C95" s="2">
         <f t="shared" si="37"/>
         <v>0.55880000000000007</v>
       </c>
@@ -50155,7 +50179,7 @@
       <c r="B96">
         <v>1.5839999999999999</v>
       </c>
-      <c r="C96" s="3">
+      <c r="C96" s="2">
         <f t="shared" si="37"/>
         <v>0.58579999999999999</v>
       </c>
@@ -50203,7 +50227,7 @@
       <c r="B97">
         <v>5.7389999999999999</v>
       </c>
-      <c r="C97" s="3">
+      <c r="C97" s="2">
         <f t="shared" si="37"/>
         <v>2.4555499999999997</v>
       </c>
@@ -50251,7 +50275,7 @@
       <c r="B98">
         <v>0.92100000000000004</v>
       </c>
-      <c r="C98" s="3">
+      <c r="C98" s="2">
         <f t="shared" si="37"/>
         <v>0.28745000000000004</v>
       </c>
@@ -50299,7 +50323,7 @@
       <c r="B99">
         <v>1.5409999999999999</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99" s="2">
         <f t="shared" si="37"/>
         <v>0.56645000000000001</v>
       </c>
@@ -50347,7 +50371,7 @@
       <c r="B100">
         <v>0.84699999999999998</v>
       </c>
-      <c r="C100" s="3">
+      <c r="C100" s="2">
         <f t="shared" si="37"/>
         <v>0.25414999999999999</v>
       </c>
@@ -50395,7 +50419,7 @@
       <c r="B101">
         <v>0.95599999999999996</v>
       </c>
-      <c r="C101" s="3">
+      <c r="C101" s="2">
         <f t="shared" si="37"/>
         <v>0.30319999999999997</v>
       </c>
@@ -50443,7 +50467,7 @@
       <c r="B102">
         <v>3.8940000000000001</v>
       </c>
-      <c r="C102" s="3">
+      <c r="C102" s="2">
         <f t="shared" si="37"/>
         <v>1.6253000000000002</v>
       </c>
@@ -50491,7 +50515,7 @@
       <c r="B103">
         <v>3.4079999999999999</v>
       </c>
-      <c r="C103" s="3">
+      <c r="C103" s="2">
         <f t="shared" si="37"/>
         <v>1.4066000000000001</v>
       </c>
@@ -50539,7 +50563,7 @@
       <c r="B104">
         <v>3.3380000000000001</v>
       </c>
-      <c r="C104" s="3">
+      <c r="C104" s="2">
         <f t="shared" si="37"/>
         <v>1.3751</v>
       </c>
@@ -50587,7 +50611,7 @@
       <c r="B105">
         <v>3.0089999999999999</v>
       </c>
-      <c r="C105" s="3">
+      <c r="C105" s="2">
         <f t="shared" si="37"/>
         <v>1.22705</v>
       </c>
@@ -50656,7 +50680,7 @@
       <c r="B106">
         <v>0.60499999999999998</v>
       </c>
-      <c r="C106" s="3">
+      <c r="C106" s="2">
         <f t="shared" si="37"/>
         <v>0.14524999999999999</v>
       </c>
@@ -50734,7 +50758,7 @@
       <c r="B107">
         <v>2.9740000000000002</v>
       </c>
-      <c r="C107" s="3">
+      <c r="C107" s="2">
         <f t="shared" si="37"/>
         <v>1.2113</v>
       </c>
@@ -50813,7 +50837,7 @@
       <c r="B108">
         <v>4.234</v>
       </c>
-      <c r="C108" s="3">
+      <c r="C108" s="2">
         <f t="shared" si="37"/>
         <v>1.7783</v>
       </c>
@@ -50892,7 +50916,7 @@
       <c r="B109">
         <v>0.95799999999999996</v>
       </c>
-      <c r="C109" s="3">
+      <c r="C109" s="2">
         <f t="shared" si="37"/>
         <v>0.30409999999999998</v>
       </c>
@@ -50971,7 +50995,7 @@
       <c r="B110">
         <v>0.77100000000000002</v>
       </c>
-      <c r="C110" s="3">
+      <c r="C110" s="2">
         <f t="shared" si="37"/>
         <v>0.21995000000000003</v>
       </c>
@@ -51050,7 +51074,7 @@
       <c r="B111">
         <v>2.1349999999999998</v>
       </c>
-      <c r="C111" s="3">
+      <c r="C111" s="2">
         <f t="shared" si="37"/>
         <v>0.83374999999999988</v>
       </c>
@@ -51129,7 +51153,7 @@
       <c r="B112">
         <v>1.649</v>
       </c>
-      <c r="C112" s="3">
+      <c r="C112" s="2">
         <f t="shared" si="37"/>
         <v>0.61504999999999999</v>
       </c>
@@ -51208,7 +51232,7 @@
       <c r="B113">
         <v>2.3529999999999998</v>
       </c>
-      <c r="C113" s="3">
+      <c r="C113" s="2">
         <f t="shared" si="37"/>
         <v>0.93184999999999985</v>
       </c>
@@ -51287,7 +51311,7 @@
       <c r="B114">
         <v>1.5940000000000001</v>
       </c>
-      <c r="C114" s="3">
+      <c r="C114" s="2">
         <f t="shared" si="37"/>
         <v>0.59030000000000005</v>
       </c>
@@ -51366,7 +51390,7 @@
       <c r="B115">
         <v>3.145</v>
       </c>
-      <c r="C115" s="3">
+      <c r="C115" s="2">
         <f t="shared" si="37"/>
         <v>1.2882500000000001</v>
       </c>
@@ -51445,7 +51469,7 @@
       <c r="B116">
         <v>6.976</v>
       </c>
-      <c r="C116" s="3">
+      <c r="C116" s="2">
         <f t="shared" si="37"/>
         <v>3.0122</v>
       </c>
@@ -51524,7 +51548,7 @@
       <c r="B117">
         <v>4.1349999999999998</v>
       </c>
-      <c r="C117" s="3">
+      <c r="C117" s="2">
         <f t="shared" si="37"/>
         <v>1.7337499999999999</v>
       </c>
@@ -51603,7 +51627,7 @@
       <c r="B118">
         <v>4.1659999999999995</v>
       </c>
-      <c r="C118" s="3">
+      <c r="C118" s="2">
         <f t="shared" si="37"/>
         <v>1.7476999999999998</v>
       </c>
@@ -51682,7 +51706,7 @@
       <c r="B119">
         <v>2.6970000000000001</v>
       </c>
-      <c r="C119" s="3">
+      <c r="C119" s="2">
         <f t="shared" si="37"/>
         <v>1.0866500000000001</v>
       </c>
@@ -51761,7 +51785,7 @@
       <c r="B120">
         <v>8.4710000000000001</v>
       </c>
-      <c r="C120" s="3">
+      <c r="C120" s="2">
         <f t="shared" si="37"/>
         <v>3.6849499999999997</v>
       </c>
@@ -51840,7 +51864,7 @@
       <c r="B121">
         <v>3.2649999999999997</v>
       </c>
-      <c r="C121" s="3">
+      <c r="C121" s="2">
         <f t="shared" si="37"/>
         <v>1.3422499999999999</v>
       </c>
@@ -51919,7 +51943,7 @@
       <c r="B122">
         <v>0.70699999999999996</v>
       </c>
-      <c r="C122" s="3">
+      <c r="C122" s="2">
         <f t="shared" si="37"/>
         <v>0.19114999999999999</v>
       </c>
@@ -51998,7 +52022,7 @@
       <c r="B123">
         <v>2.024</v>
       </c>
-      <c r="C123" s="3">
+      <c r="C123" s="2">
         <f t="shared" si="37"/>
         <v>0.78380000000000005</v>
       </c>
@@ -52077,7 +52101,7 @@
       <c r="B124">
         <v>4.5620000000000003</v>
       </c>
-      <c r="C124" s="3">
+      <c r="C124" s="2">
         <f t="shared" si="37"/>
         <v>1.9259000000000002</v>
       </c>
@@ -52156,7 +52180,7 @@
       <c r="B125">
         <v>4.0720000000000001</v>
       </c>
-      <c r="C125" s="3">
+      <c r="C125" s="2">
         <f t="shared" si="37"/>
         <v>1.7054</v>
       </c>
@@ -52235,7 +52259,7 @@
       <c r="B126">
         <v>5.59</v>
       </c>
-      <c r="C126" s="3">
+      <c r="C126" s="2">
         <f t="shared" si="37"/>
         <v>2.3884999999999996</v>
       </c>
@@ -52314,7 +52338,7 @@
       <c r="B127">
         <v>3.7709999999999999</v>
       </c>
-      <c r="C127" s="3">
+      <c r="C127" s="2">
         <f t="shared" si="37"/>
         <v>1.56995</v>
       </c>
@@ -52393,7 +52417,7 @@
       <c r="B128">
         <v>0.57799999999999996</v>
       </c>
-      <c r="C128" s="3">
+      <c r="C128" s="2">
         <f t="shared" si="37"/>
         <v>0.1331</v>
       </c>
@@ -52472,7 +52496,7 @@
       <c r="B129">
         <v>7.04</v>
       </c>
-      <c r="C129" s="3">
+      <c r="C129" s="2">
         <f t="shared" si="37"/>
         <v>3.0410000000000004</v>
       </c>
@@ -52551,7 +52575,7 @@
       <c r="B130">
         <v>11.260999999999999</v>
       </c>
-      <c r="C130" s="3">
+      <c r="C130" s="2">
         <f t="shared" si="37"/>
         <v>4.9404500000000002</v>
       </c>
@@ -52630,7 +52654,7 @@
       <c r="B131">
         <v>2.9780000000000002</v>
       </c>
-      <c r="C131" s="3">
+      <c r="C131" s="2">
         <f t="shared" si="37"/>
         <v>1.2131000000000001</v>
       </c>
@@ -52709,7 +52733,7 @@
       <c r="B132">
         <v>2.4550000000000001</v>
       </c>
-      <c r="C132" s="3">
+      <c r="C132" s="2">
         <f t="shared" ref="C132:C195" si="55">(0.45*B132)-0.127</f>
         <v>0.97775000000000012</v>
       </c>
@@ -52788,7 +52812,7 @@
       <c r="B133">
         <v>3.2749999999999999</v>
       </c>
-      <c r="C133" s="3">
+      <c r="C133" s="2">
         <f t="shared" si="55"/>
         <v>1.3467499999999999</v>
       </c>
@@ -52867,7 +52891,7 @@
       <c r="B134">
         <v>3.1349999999999998</v>
       </c>
-      <c r="C134" s="3">
+      <c r="C134" s="2">
         <f t="shared" si="55"/>
         <v>1.2837499999999999</v>
       </c>
@@ -52946,7 +52970,7 @@
       <c r="B135">
         <v>0.46700000000000003</v>
       </c>
-      <c r="C135" s="3">
+      <c r="C135" s="2">
         <f t="shared" si="55"/>
         <v>8.3150000000000002E-2</v>
       </c>
@@ -53025,7 +53049,7 @@
       <c r="B136">
         <v>0.84399999999999997</v>
       </c>
-      <c r="C136" s="3">
+      <c r="C136" s="2">
         <f t="shared" si="55"/>
         <v>0.25279999999999997</v>
       </c>
@@ -53104,7 +53128,7 @@
       <c r="B137">
         <v>2.677</v>
       </c>
-      <c r="C137" s="3">
+      <c r="C137" s="2">
         <f t="shared" si="55"/>
         <v>1.07765</v>
       </c>
@@ -53183,7 +53207,7 @@
       <c r="B138">
         <v>2.25</v>
       </c>
-      <c r="C138" s="3">
+      <c r="C138" s="2">
         <f t="shared" si="55"/>
         <v>0.88549999999999995</v>
       </c>
@@ -53262,7 +53286,7 @@
       <c r="B139">
         <v>3.3210000000000002</v>
       </c>
-      <c r="C139" s="3">
+      <c r="C139" s="2">
         <f t="shared" si="55"/>
         <v>1.3674500000000001</v>
       </c>
@@ -53341,7 +53365,7 @@
       <c r="B140">
         <v>1.0029999999999999</v>
       </c>
-      <c r="C140" s="3">
+      <c r="C140" s="2">
         <f t="shared" si="55"/>
         <v>0.32434999999999997</v>
       </c>
@@ -53420,7 +53444,7 @@
       <c r="B141">
         <v>1.6950000000000001</v>
       </c>
-      <c r="C141" s="3">
+      <c r="C141" s="2">
         <f t="shared" si="55"/>
         <v>0.63575000000000004</v>
       </c>
@@ -53499,7 +53523,7 @@
       <c r="B142">
         <v>4.3479999999999999</v>
       </c>
-      <c r="C142" s="3">
+      <c r="C142" s="2">
         <f t="shared" si="55"/>
         <v>1.8295999999999999</v>
       </c>
@@ -53578,7 +53602,7 @@
       <c r="B143">
         <v>6.3019999999999996</v>
       </c>
-      <c r="C143" s="3">
+      <c r="C143" s="2">
         <f t="shared" si="55"/>
         <v>2.7088999999999999</v>
       </c>
@@ -53657,7 +53681,7 @@
       <c r="B144">
         <v>6.1349999999999998</v>
       </c>
-      <c r="C144" s="3">
+      <c r="C144" s="2">
         <f t="shared" si="55"/>
         <v>2.63375</v>
       </c>
@@ -53736,7 +53760,7 @@
       <c r="B145">
         <v>5.29</v>
       </c>
-      <c r="C145" s="3">
+      <c r="C145" s="2">
         <f t="shared" si="55"/>
         <v>2.2534999999999998</v>
       </c>
@@ -53784,7 +53808,7 @@
       <c r="B146">
         <v>3.6480000000000001</v>
       </c>
-      <c r="C146" s="3">
+      <c r="C146" s="2">
         <f t="shared" si="55"/>
         <v>1.5146000000000002</v>
       </c>
@@ -53832,7 +53856,7 @@
       <c r="B147">
         <v>1.343</v>
       </c>
-      <c r="C147" s="3">
+      <c r="C147" s="2">
         <f t="shared" si="55"/>
         <v>0.47735000000000005</v>
       </c>
@@ -53880,7 +53904,7 @@
       <c r="B148">
         <v>2.714</v>
       </c>
-      <c r="C148" s="3">
+      <c r="C148" s="2">
         <f t="shared" si="55"/>
         <v>1.0943000000000001</v>
       </c>
@@ -53928,7 +53952,7 @@
       <c r="B149">
         <v>3.6609999999999996</v>
       </c>
-      <c r="C149" s="3">
+      <c r="C149" s="2">
         <f t="shared" si="55"/>
         <v>1.5204499999999999</v>
       </c>
@@ -53976,7 +54000,7 @@
       <c r="B150">
         <v>6.9660000000000011</v>
       </c>
-      <c r="C150" s="3">
+      <c r="C150" s="2">
         <f t="shared" si="55"/>
         <v>3.0077000000000007</v>
       </c>
@@ -54024,7 +54048,7 @@
       <c r="B151">
         <v>4.9050000000000002</v>
       </c>
-      <c r="C151" s="3">
+      <c r="C151" s="2">
         <f t="shared" si="55"/>
         <v>2.0802500000000004</v>
       </c>
@@ -54072,7 +54096,7 @@
       <c r="B152">
         <v>1.8770000000000002</v>
       </c>
-      <c r="C152" s="3">
+      <c r="C152" s="2">
         <f t="shared" si="55"/>
         <v>0.71765000000000012</v>
       </c>
@@ -54120,7 +54144,7 @@
       <c r="B153">
         <v>1.107</v>
       </c>
-      <c r="C153" s="3">
+      <c r="C153" s="2">
         <f t="shared" si="55"/>
         <v>0.37114999999999998</v>
       </c>
@@ -54168,7 +54192,7 @@
       <c r="B154">
         <v>0.98699999999999999</v>
       </c>
-      <c r="C154" s="3">
+      <c r="C154" s="2">
         <f t="shared" si="55"/>
         <v>0.31714999999999999</v>
       </c>
@@ -54216,7 +54240,7 @@
       <c r="B155">
         <v>1.4990000000000001</v>
       </c>
-      <c r="C155" s="3">
+      <c r="C155" s="2">
         <f t="shared" si="55"/>
         <v>0.54755000000000009</v>
       </c>
@@ -54264,7 +54288,7 @@
       <c r="B156">
         <v>2.012</v>
       </c>
-      <c r="C156" s="3">
+      <c r="C156" s="2">
         <f t="shared" si="55"/>
         <v>0.77839999999999998</v>
       </c>
@@ -54312,7 +54336,7 @@
       <c r="B157">
         <v>0.79500000000000004</v>
       </c>
-      <c r="C157" s="3">
+      <c r="C157" s="2">
         <f t="shared" si="55"/>
         <v>0.23075000000000001</v>
       </c>
@@ -54360,7 +54384,7 @@
       <c r="B158">
         <v>4.3550000000000004</v>
       </c>
-      <c r="C158" s="3">
+      <c r="C158" s="2">
         <f t="shared" si="55"/>
         <v>1.8327500000000003</v>
       </c>
@@ -54408,7 +54432,7 @@
       <c r="B159">
         <v>3.3650000000000002</v>
       </c>
-      <c r="C159" s="3">
+      <c r="C159" s="2">
         <f t="shared" si="55"/>
         <v>1.3872500000000001</v>
       </c>
@@ -54456,7 +54480,7 @@
       <c r="B160">
         <v>4.2010000000000005</v>
       </c>
-      <c r="C160" s="3">
+      <c r="C160" s="2">
         <f t="shared" si="55"/>
         <v>1.7634500000000002</v>
       </c>
@@ -54504,7 +54528,7 @@
       <c r="B161">
         <v>4.7379999999999995</v>
       </c>
-      <c r="C161" s="3">
+      <c r="C161" s="2">
         <f t="shared" si="55"/>
         <v>2.0050999999999997</v>
       </c>
@@ -54552,7 +54576,7 @@
       <c r="B162">
         <v>3.3239999999999998</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C162" s="2">
         <f t="shared" si="55"/>
         <v>1.3688</v>
       </c>
@@ -54600,7 +54624,7 @@
       <c r="B163">
         <v>3.5960000000000001</v>
       </c>
-      <c r="C163" s="3">
+      <c r="C163" s="2">
         <f t="shared" si="55"/>
         <v>1.4912000000000001</v>
       </c>
@@ -54648,7 +54672,7 @@
       <c r="B164">
         <v>2.802</v>
       </c>
-      <c r="C164" s="3">
+      <c r="C164" s="2">
         <f t="shared" si="55"/>
         <v>1.1339000000000001</v>
       </c>
@@ -54696,7 +54720,7 @@
       <c r="B165">
         <v>2.7720000000000002</v>
       </c>
-      <c r="C165" s="3">
+      <c r="C165" s="2">
         <f t="shared" si="55"/>
         <v>1.1204000000000001</v>
       </c>
@@ -54744,7 +54768,7 @@
       <c r="B166">
         <v>3.5609999999999999</v>
       </c>
-      <c r="C166" s="3">
+      <c r="C166" s="2">
         <f t="shared" si="55"/>
         <v>1.4754499999999999</v>
       </c>
@@ -54792,7 +54816,7 @@
       <c r="B167">
         <v>1.863</v>
       </c>
-      <c r="C167" s="3">
+      <c r="C167" s="2">
         <f t="shared" si="55"/>
         <v>0.71135000000000004</v>
       </c>
@@ -54840,7 +54864,7 @@
       <c r="B168">
         <v>0.79200000000000004</v>
       </c>
-      <c r="C168" s="3">
+      <c r="C168" s="2">
         <f t="shared" si="55"/>
         <v>0.22940000000000005</v>
       </c>
@@ -54888,7 +54912,7 @@
       <c r="B169">
         <v>3.3180000000000001</v>
       </c>
-      <c r="C169" s="3">
+      <c r="C169" s="2">
         <f t="shared" si="55"/>
         <v>1.3661000000000001</v>
       </c>
@@ -54936,7 +54960,7 @@
       <c r="B170">
         <v>3.2149999999999999</v>
       </c>
-      <c r="C170" s="3">
+      <c r="C170" s="2">
         <f t="shared" si="55"/>
         <v>1.31975</v>
       </c>
@@ -54984,7 +55008,7 @@
       <c r="B171">
         <v>5.2</v>
       </c>
-      <c r="C171" s="3">
+      <c r="C171" s="2">
         <f t="shared" si="55"/>
         <v>2.2130000000000001</v>
       </c>
@@ -55032,7 +55056,7 @@
       <c r="B172">
         <v>1.4910000000000001</v>
       </c>
-      <c r="C172" s="3">
+      <c r="C172" s="2">
         <f t="shared" si="55"/>
         <v>0.54395000000000004</v>
       </c>
@@ -55080,7 +55104,7 @@
       <c r="B173">
         <v>3.476</v>
       </c>
-      <c r="C173" s="3">
+      <c r="C173" s="2">
         <f t="shared" si="55"/>
         <v>1.4372</v>
       </c>
@@ -55128,7 +55152,7 @@
       <c r="B174">
         <v>0.76300000000000001</v>
       </c>
-      <c r="C174" s="3">
+      <c r="C174" s="2">
         <f t="shared" si="55"/>
         <v>0.21634999999999999</v>
       </c>
@@ -55176,7 +55200,7 @@
       <c r="B175">
         <v>0.77800000000000002</v>
       </c>
-      <c r="C175" s="3">
+      <c r="C175" s="2">
         <f t="shared" si="55"/>
         <v>0.22310000000000002</v>
       </c>
@@ -55224,7 +55248,7 @@
       <c r="B176">
         <v>0.68799999999999994</v>
       </c>
-      <c r="C176" s="3">
+      <c r="C176" s="2">
         <f t="shared" si="55"/>
         <v>0.18259999999999998</v>
       </c>
@@ -55272,7 +55296,7 @@
       <c r="B177">
         <v>0.85399999999999998</v>
       </c>
-      <c r="C177" s="3">
+      <c r="C177" s="2">
         <f t="shared" si="55"/>
         <v>0.25729999999999997</v>
       </c>
@@ -55320,7 +55344,7 @@
       <c r="B178">
         <v>2.5459999999999998</v>
       </c>
-      <c r="C178" s="3">
+      <c r="C178" s="2">
         <f t="shared" si="55"/>
         <v>1.0186999999999999</v>
       </c>
@@ -55368,7 +55392,7 @@
       <c r="B179">
         <v>0.85099999999999998</v>
       </c>
-      <c r="C179" s="3">
+      <c r="C179" s="2">
         <f t="shared" si="55"/>
         <v>0.25595000000000001</v>
       </c>
@@ -55416,7 +55440,7 @@
       <c r="B180">
         <v>3.3220000000000001</v>
       </c>
-      <c r="C180" s="3">
+      <c r="C180" s="2">
         <f t="shared" si="55"/>
         <v>1.3679000000000001</v>
       </c>
@@ -55464,7 +55488,7 @@
       <c r="B181">
         <v>0.879</v>
       </c>
-      <c r="C181" s="3">
+      <c r="C181" s="2">
         <f t="shared" si="55"/>
         <v>0.26855000000000001</v>
       </c>
@@ -55512,7 +55536,7 @@
       <c r="B182">
         <v>3.0630000000000002</v>
       </c>
-      <c r="C182" s="3">
+      <c r="C182" s="2">
         <f t="shared" si="55"/>
         <v>1.2513500000000002</v>
       </c>
@@ -55560,7 +55584,7 @@
       <c r="B183">
         <v>0.79900000000000004</v>
       </c>
-      <c r="C183" s="3">
+      <c r="C183" s="2">
         <f t="shared" si="55"/>
         <v>0.23255000000000003</v>
       </c>
@@ -55608,7 +55632,7 @@
       <c r="B184">
         <v>0.88200000000000001</v>
       </c>
-      <c r="C184" s="3">
+      <c r="C184" s="2">
         <f t="shared" si="55"/>
         <v>0.26990000000000003</v>
       </c>
@@ -55656,7 +55680,7 @@
       <c r="B185">
         <v>2.9929999999999999</v>
       </c>
-      <c r="C185" s="3">
+      <c r="C185" s="2">
         <f t="shared" si="55"/>
         <v>1.2198499999999999</v>
       </c>
@@ -55704,7 +55728,7 @@
       <c r="B186">
         <v>3.1669999999999998</v>
       </c>
-      <c r="C186" s="3">
+      <c r="C186" s="2">
         <f t="shared" si="55"/>
         <v>1.2981499999999999</v>
       </c>
@@ -55752,7 +55776,7 @@
       <c r="B187">
         <v>1.9369999999999998</v>
       </c>
-      <c r="C187" s="3">
+      <c r="C187" s="2">
         <f t="shared" si="55"/>
         <v>0.74464999999999992</v>
       </c>
@@ -55800,7 +55824,7 @@
       <c r="B188">
         <v>2.1880000000000002</v>
       </c>
-      <c r="C188" s="3">
+      <c r="C188" s="2">
         <f t="shared" si="55"/>
         <v>0.85760000000000014</v>
       </c>
@@ -55848,7 +55872,7 @@
       <c r="B189">
         <v>3.7919999999999998</v>
       </c>
-      <c r="C189" s="3">
+      <c r="C189" s="2">
         <f t="shared" si="55"/>
         <v>1.5793999999999999</v>
       </c>
@@ -55896,7 +55920,7 @@
       <c r="B190">
         <v>1.742</v>
       </c>
-      <c r="C190" s="3">
+      <c r="C190" s="2">
         <f t="shared" si="55"/>
         <v>0.65690000000000004</v>
       </c>
@@ -55944,7 +55968,7 @@
       <c r="B191">
         <v>1.8089999999999999</v>
       </c>
-      <c r="C191" s="3">
+      <c r="C191" s="2">
         <f t="shared" si="55"/>
         <v>0.68704999999999994</v>
       </c>
@@ -55992,7 +56016,7 @@
       <c r="B192">
         <v>1.0169999999999999</v>
       </c>
-      <c r="C192" s="3">
+      <c r="C192" s="2">
         <f t="shared" si="55"/>
         <v>0.33064999999999994</v>
       </c>
@@ -56040,7 +56064,7 @@
       <c r="B193">
         <v>1.5409999999999999</v>
       </c>
-      <c r="C193" s="3">
+      <c r="C193" s="2">
         <f t="shared" si="55"/>
         <v>0.56645000000000001</v>
       </c>
@@ -56088,7 +56112,7 @@
       <c r="B194">
         <v>1.875</v>
       </c>
-      <c r="C194" s="3">
+      <c r="C194" s="2">
         <f t="shared" si="55"/>
         <v>0.71675</v>
       </c>
@@ -56136,7 +56160,7 @@
       <c r="B195">
         <v>1.9710000000000001</v>
       </c>
-      <c r="C195" s="3">
+      <c r="C195" s="2">
         <f t="shared" si="55"/>
         <v>0.75995000000000001</v>
       </c>
@@ -56184,7 +56208,7 @@
       <c r="B196">
         <v>2.3450000000000002</v>
       </c>
-      <c r="C196" s="3">
+      <c r="C196" s="2">
         <f t="shared" ref="C196:C245" si="65">(0.45*B196)-0.127</f>
         <v>0.92825000000000002</v>
       </c>
@@ -56232,7 +56256,7 @@
       <c r="B197">
         <v>1.621</v>
       </c>
-      <c r="C197" s="3">
+      <c r="C197" s="2">
         <f t="shared" si="65"/>
         <v>0.60245000000000004</v>
       </c>
@@ -56280,7 +56304,7 @@
       <c r="B198">
         <v>2.6859999999999999</v>
       </c>
-      <c r="C198" s="3">
+      <c r="C198" s="2">
         <f t="shared" si="65"/>
         <v>1.0817000000000001</v>
       </c>
@@ -56328,7 +56352,7 @@
       <c r="B199">
         <v>1.552</v>
       </c>
-      <c r="C199" s="3">
+      <c r="C199" s="2">
         <f t="shared" si="65"/>
         <v>0.57140000000000002</v>
       </c>
@@ -56376,7 +56400,7 @@
       <c r="B200">
         <v>0.90500000000000003</v>
       </c>
-      <c r="C200" s="3">
+      <c r="C200" s="2">
         <f t="shared" si="65"/>
         <v>0.28025</v>
       </c>
@@ -56424,7 +56448,7 @@
       <c r="B201">
         <v>0.81299999999999994</v>
       </c>
-      <c r="C201" s="3">
+      <c r="C201" s="2">
         <f t="shared" si="65"/>
         <v>0.23885000000000001</v>
       </c>
@@ -56472,7 +56496,7 @@
       <c r="B202">
         <v>1.593</v>
       </c>
-      <c r="C202" s="3">
+      <c r="C202" s="2">
         <f t="shared" si="65"/>
         <v>0.58984999999999999</v>
       </c>
@@ -56520,7 +56544,7 @@
       <c r="B203">
         <v>0.82299999999999995</v>
       </c>
-      <c r="C203" s="3">
+      <c r="C203" s="2">
         <f t="shared" si="65"/>
         <v>0.24335000000000001</v>
       </c>
@@ -56568,7 +56592,7 @@
       <c r="B204">
         <v>1.236</v>
       </c>
-      <c r="C204" s="3">
+      <c r="C204" s="2">
         <f t="shared" si="65"/>
         <v>0.42920000000000003</v>
       </c>
@@ -56616,7 +56640,7 @@
       <c r="B205">
         <v>1.9810000000000001</v>
       </c>
-      <c r="C205" s="3">
+      <c r="C205" s="2">
         <f t="shared" si="65"/>
         <v>0.76445000000000007</v>
       </c>
@@ -56664,7 +56688,7 @@
       <c r="B206">
         <v>0.877</v>
       </c>
-      <c r="C206" s="3">
+      <c r="C206" s="2">
         <f t="shared" si="65"/>
         <v>0.26765</v>
       </c>
@@ -56712,7 +56736,7 @@
       <c r="B207">
         <v>1.2430000000000001</v>
       </c>
-      <c r="C207" s="3">
+      <c r="C207" s="2">
         <f t="shared" si="65"/>
         <v>0.43235000000000001</v>
       </c>
@@ -56760,7 +56784,7 @@
       <c r="B208">
         <v>3.91</v>
       </c>
-      <c r="C208" s="3">
+      <c r="C208" s="2">
         <f t="shared" si="65"/>
         <v>1.6325000000000001</v>
       </c>
@@ -56808,7 +56832,7 @@
       <c r="B209">
         <v>0.93700000000000006</v>
       </c>
-      <c r="C209" s="3">
+      <c r="C209" s="2">
         <f t="shared" si="65"/>
         <v>0.29465000000000002</v>
       </c>
@@ -56856,7 +56880,7 @@
       <c r="B210">
         <v>2.6579999999999999</v>
       </c>
-      <c r="C210" s="3">
+      <c r="C210" s="2">
         <f t="shared" si="65"/>
         <v>1.0690999999999999</v>
       </c>
@@ -56904,7 +56928,7 @@
       <c r="B211">
         <v>1.631</v>
       </c>
-      <c r="C211" s="3">
+      <c r="C211" s="2">
         <f t="shared" si="65"/>
         <v>0.60694999999999999</v>
       </c>
@@ -56952,7 +56976,7 @@
       <c r="B212">
         <v>1.7360000000000002</v>
       </c>
-      <c r="C212" s="3">
+      <c r="C212" s="2">
         <f t="shared" si="65"/>
         <v>0.65420000000000011</v>
       </c>
@@ -57000,7 +57024,7 @@
       <c r="B213">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C213" s="3">
+      <c r="C213" s="2">
         <f t="shared" si="65"/>
         <v>0.36800000000000005</v>
       </c>
@@ -57048,7 +57072,7 @@
       <c r="B214">
         <v>1.0660000000000001</v>
       </c>
-      <c r="C214" s="3">
+      <c r="C214" s="2">
         <f t="shared" si="65"/>
         <v>0.35270000000000001</v>
       </c>
@@ -57096,7 +57120,7 @@
       <c r="B215">
         <v>3.3470000000000004</v>
       </c>
-      <c r="C215" s="3">
+      <c r="C215" s="2">
         <f t="shared" si="65"/>
         <v>1.3791500000000003</v>
       </c>
@@ -57144,7 +57168,7 @@
       <c r="B216">
         <v>0.74299999999999999</v>
       </c>
-      <c r="C216" s="3">
+      <c r="C216" s="2">
         <f t="shared" si="65"/>
         <v>0.20734999999999998</v>
       </c>
@@ -57192,7 +57216,7 @@
       <c r="B217">
         <v>1.653</v>
       </c>
-      <c r="C217" s="3">
+      <c r="C217" s="2">
         <f t="shared" si="65"/>
         <v>0.61685000000000001</v>
       </c>
@@ -57240,7 +57264,7 @@
       <c r="B218">
         <v>1.698</v>
       </c>
-      <c r="C218" s="3">
+      <c r="C218" s="2">
         <f t="shared" si="65"/>
         <v>0.6371</v>
       </c>
@@ -57283,244 +57307,244 @@
     </row>
     <row r="219" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A219" s="1"/>
-      <c r="C219" s="3"/>
+      <c r="C219" s="2"/>
     </row>
     <row r="220" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A220" s="1"/>
-      <c r="C220" s="3"/>
+      <c r="C220" s="2"/>
     </row>
     <row r="221" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A221" s="1"/>
-      <c r="C221" s="3"/>
+      <c r="C221" s="2"/>
     </row>
     <row r="222" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A222" s="1"/>
-      <c r="C222" s="3"/>
+      <c r="C222" s="2"/>
     </row>
     <row r="223" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A223" s="10" t="s">
+      <c r="A223" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B223" s="11">
+      <c r="B223" s="10">
         <v>0.81599999999999995</v>
       </c>
-      <c r="C223" s="12">
+      <c r="C223" s="11">
         <f t="shared" si="65"/>
         <v>0.24019999999999997</v>
       </c>
-      <c r="D223" s="10">
+      <c r="D223" s="9">
         <f t="shared" si="66"/>
         <v>8.8824E-2</v>
       </c>
-      <c r="E223" s="10">
+      <c r="E223" s="9">
         <f t="shared" si="67"/>
         <v>242001499.99999994</v>
       </c>
-      <c r="F223" s="10">
+      <c r="F223" s="9">
         <f t="shared" si="68"/>
         <v>129327744</v>
       </c>
-      <c r="G223" s="10">
+      <c r="G223" s="9">
         <f t="shared" si="69"/>
         <v>0.24019999999999997</v>
       </c>
-      <c r="H223" s="10">
+      <c r="H223" s="9">
         <f>D223+H222</f>
         <v>8.8824E-2</v>
       </c>
-      <c r="I223" s="10">
+      <c r="I223" s="9">
         <f t="shared" si="71"/>
         <v>0.16451199999999999</v>
       </c>
-      <c r="J223" s="10">
+      <c r="J223" s="9">
         <f>E223+J222</f>
         <v>242001499.99999994</v>
       </c>
-      <c r="K223" s="10">
+      <c r="K223" s="9">
         <f>F223+K222</f>
         <v>129327744</v>
       </c>
-      <c r="L223" s="10">
+      <c r="L223" s="9">
         <f t="shared" si="74"/>
         <v>185664621.99999997</v>
       </c>
-      <c r="M223" s="10" t="s">
+      <c r="M223" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="N223" s="10">
+      <c r="N223" s="9">
         <v>0</v>
       </c>
-      <c r="O223" s="10">
+      <c r="O223" s="9">
         <f t="shared" ref="O223:O245" si="75">(N223*C223)+O222</f>
         <v>0</v>
       </c>
-      <c r="P223" s="10">
+      <c r="P223" s="9">
         <f t="shared" ref="P223:P245" si="76">(N223*D223)+P222</f>
         <v>0</v>
       </c>
-      <c r="Q223" s="10">
+      <c r="Q223" s="9">
         <f t="shared" ref="Q223:Q245" si="77">(O223+P223)/2</f>
         <v>0</v>
       </c>
-      <c r="R223" s="10">
+      <c r="R223" s="9">
         <f t="shared" ref="R223:R245" si="78">(N223*F223)+R222</f>
         <v>0</v>
       </c>
-      <c r="S223" s="10">
+      <c r="S223" s="9">
         <f t="shared" ref="S223:S245" si="79">(N223*G223)+S222</f>
         <v>0</v>
       </c>
-      <c r="T223" s="10">
+      <c r="T223" s="9">
         <f t="shared" ref="T223:T245" si="80">(R223+S223)/2</f>
         <v>0</v>
       </c>
-      <c r="U223" s="10"/>
-      <c r="V223" s="10" t="s">
+      <c r="U223" s="9"/>
+      <c r="V223" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="W223" s="10">
+      <c r="W223" s="9">
         <v>0</v>
       </c>
-      <c r="X223" s="10">
+      <c r="X223" s="9">
         <v>0.2402</v>
       </c>
-      <c r="Y223" s="10">
+      <c r="Y223" s="9">
         <v>8.8824E-2</v>
       </c>
-      <c r="Z223" s="10">
+      <c r="Z223" s="9">
         <v>0.16451199999999999</v>
       </c>
-      <c r="AA223" s="10">
+      <c r="AA223" s="9">
         <v>242001500</v>
       </c>
-      <c r="AB223" s="10">
+      <c r="AB223" s="9">
         <v>129327744</v>
       </c>
-      <c r="AC223" s="10">
+      <c r="AC223" s="9">
         <v>185664622</v>
       </c>
-      <c r="AD223" s="10"/>
+      <c r="AD223" s="9"/>
     </row>
     <row r="224" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A224" s="10" t="s">
+      <c r="A224" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B224" s="11">
+      <c r="B224" s="10">
         <v>0.89600000000000002</v>
       </c>
-      <c r="C224" s="12">
+      <c r="C224" s="11">
         <f t="shared" si="65"/>
         <v>0.2762</v>
       </c>
-      <c r="D224" s="10">
+      <c r="D224" s="9">
         <f t="shared" si="66"/>
         <v>0.10194400000000002</v>
       </c>
-      <c r="E224" s="10">
+      <c r="E224" s="9">
         <f t="shared" si="67"/>
         <v>278271500</v>
       </c>
-      <c r="F224" s="10">
+      <c r="F224" s="9">
         <f t="shared" si="68"/>
         <v>148430464.00000003</v>
       </c>
-      <c r="G224" s="10">
+      <c r="G224" s="9">
         <f t="shared" si="69"/>
         <v>0.51639999999999997</v>
       </c>
-      <c r="H224" s="10">
+      <c r="H224" s="9">
         <f t="shared" si="70"/>
         <v>0.19076800000000002</v>
       </c>
-      <c r="I224" s="10">
+      <c r="I224" s="9">
         <f t="shared" si="71"/>
         <v>0.35358400000000001</v>
       </c>
-      <c r="J224" s="10">
+      <c r="J224" s="9">
         <f t="shared" si="72"/>
         <v>520272999.99999994</v>
       </c>
-      <c r="K224" s="10">
+      <c r="K224" s="9">
         <f t="shared" si="73"/>
         <v>277758208</v>
       </c>
-      <c r="L224" s="10">
+      <c r="L224" s="9">
         <f t="shared" si="74"/>
         <v>399015604</v>
       </c>
-      <c r="M224" s="10" t="s">
+      <c r="M224" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="N224" s="10">
+      <c r="N224" s="9">
         <f>ABS((M224-M223)*24*60*60)</f>
         <v>25200.000000419095</v>
       </c>
-      <c r="O224" s="10">
+      <c r="O224" s="9">
         <f t="shared" si="75"/>
         <v>6960.2400001157539</v>
       </c>
-      <c r="P224" s="10">
+      <c r="P224" s="9">
         <f t="shared" si="76"/>
         <v>2568.988800042725</v>
       </c>
-      <c r="Q224" s="10">
+      <c r="Q224" s="9">
         <f t="shared" si="77"/>
         <v>4764.6144000792392</v>
       </c>
-      <c r="R224" s="10">
+      <c r="R224" s="9">
         <f t="shared" si="78"/>
         <v>3740447692862.207</v>
       </c>
-      <c r="S224" s="10">
+      <c r="S224" s="9">
         <f t="shared" si="79"/>
         <v>13013.28000021642</v>
       </c>
-      <c r="T224" s="10">
+      <c r="T224" s="9">
         <f t="shared" si="80"/>
         <v>1870223852937.7434</v>
       </c>
-      <c r="U224" s="10"/>
-      <c r="V224" s="10" t="s">
+      <c r="U224" s="9"/>
+      <c r="V224" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="W224" s="10">
+      <c r="W224" s="9">
         <f>ABS((V224-V223)*24*60*60)</f>
         <v>25200.000000419095</v>
       </c>
-      <c r="X224" s="10">
-        <f t="shared" ref="X223:X231" si="81">(W224*C223)+X223</f>
+      <c r="X224" s="9">
+        <f t="shared" ref="X224:X231" si="81">(W224*C223)+X223</f>
         <v>6053.2802001006658</v>
       </c>
-      <c r="Y224" s="10">
-        <f t="shared" ref="Y223:Y231" si="82">(W224*D223)+Y223</f>
+      <c r="Y224" s="9">
+        <f t="shared" ref="Y224:Y231" si="82">(W224*D223)+Y223</f>
         <v>2238.4536240372258</v>
       </c>
-      <c r="Z224" s="10">
-        <f t="shared" ref="Z223:Z231" si="83">(X224+Y224)/2</f>
+      <c r="Z224" s="9">
+        <f t="shared" ref="Z224:Z231" si="83">(X224+Y224)/2</f>
         <v>4145.8669120689456</v>
       </c>
-      <c r="AA224" s="10">
-        <f t="shared" ref="AA223:AA231" si="84">(W224*E223)+AA223</f>
+      <c r="AA224" s="9">
+        <f t="shared" ref="AA224:AA231" si="84">(W224*E223)+AA223</f>
         <v>6098679801601.4199</v>
       </c>
-      <c r="AB224" s="10">
-        <f t="shared" ref="AB223:AB231" si="85">(W224*F223)+AB223</f>
+      <c r="AB224" s="9">
+        <f t="shared" ref="AB224:AB231" si="85">(W224*F223)+AB223</f>
         <v>3259188476598.2007</v>
       </c>
-      <c r="AC224" s="10">
-        <f t="shared" ref="AC223:AC231" si="86">(AA224+AB224)/2</f>
+      <c r="AC224" s="9">
+        <f t="shared" ref="AC224:AC231" si="86">(AA224+AB224)/2</f>
         <v>4678934139099.8105</v>
       </c>
-      <c r="AD224" s="10"/>
+      <c r="AD224" s="9"/>
     </row>
     <row r="225" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>52</v>
       </c>
-      <c r="B225" s="9">
+      <c r="B225" s="8">
         <v>1.0409999999999999</v>
       </c>
-      <c r="C225" s="3">
+      <c r="C225" s="2">
         <f t="shared" si="65"/>
         <v>0.34144999999999998</v>
       </c>
@@ -57627,10 +57651,10 @@
       <c r="A226" t="s">
         <v>53</v>
       </c>
-      <c r="B226" s="9">
+      <c r="B226" s="8">
         <v>2.4660000000000002</v>
       </c>
-      <c r="C226" s="3">
+      <c r="C226" s="2">
         <f t="shared" si="65"/>
         <v>0.98270000000000013</v>
       </c>
@@ -57737,10 +57761,10 @@
       <c r="A227" t="s">
         <v>54</v>
       </c>
-      <c r="B227" s="9">
+      <c r="B227" s="8">
         <v>1.5269999999999999</v>
       </c>
-      <c r="C227" s="3">
+      <c r="C227" s="2">
         <f t="shared" si="65"/>
         <v>0.56014999999999993</v>
       </c>
@@ -57847,10 +57871,10 @@
       <c r="A228" t="s">
         <v>55</v>
       </c>
-      <c r="B228" s="9">
+      <c r="B228" s="8">
         <v>3.0760000000000001</v>
       </c>
-      <c r="C228" s="3">
+      <c r="C228" s="2">
         <f t="shared" si="65"/>
         <v>1.2572000000000001</v>
       </c>
@@ -57957,10 +57981,10 @@
       <c r="A229" t="s">
         <v>56</v>
       </c>
-      <c r="B229" s="9">
+      <c r="B229" s="8">
         <v>0.89600000000000002</v>
       </c>
-      <c r="C229" s="3">
+      <c r="C229" s="2">
         <f t="shared" si="65"/>
         <v>0.2762</v>
       </c>
@@ -58067,10 +58091,10 @@
       <c r="A230" t="s">
         <v>57</v>
       </c>
-      <c r="B230" s="9">
+      <c r="B230" s="8">
         <v>0.83</v>
       </c>
-      <c r="C230" s="3">
+      <c r="C230" s="2">
         <f t="shared" si="65"/>
         <v>0.2465</v>
       </c>
@@ -58177,10 +58201,10 @@
       <c r="A231" t="s">
         <v>58</v>
       </c>
-      <c r="B231" s="9">
+      <c r="B231" s="8">
         <v>1.1479999999999999</v>
       </c>
-      <c r="C231" s="3">
+      <c r="C231" s="2">
         <f t="shared" si="65"/>
         <v>0.38959999999999995</v>
       </c>
@@ -58287,10 +58311,10 @@
       <c r="A232" t="s">
         <v>59</v>
       </c>
-      <c r="B232" s="9">
+      <c r="B232" s="8">
         <v>0.99299999999999999</v>
       </c>
-      <c r="C232" s="3">
+      <c r="C232" s="2">
         <f t="shared" si="65"/>
         <v>0.31985000000000002</v>
       </c>
@@ -58397,10 +58421,10 @@
       <c r="A233" t="s">
         <v>60</v>
       </c>
-      <c r="B233" s="9">
+      <c r="B233" s="8">
         <v>1.0469999999999999</v>
       </c>
-      <c r="C233" s="3">
+      <c r="C233" s="2">
         <f t="shared" si="65"/>
         <v>0.34414999999999996</v>
       </c>
@@ -58507,10 +58531,10 @@
       <c r="A234" t="s">
         <v>61</v>
       </c>
-      <c r="B234" s="9">
+      <c r="B234" s="8">
         <v>2.1320000000000001</v>
       </c>
-      <c r="C234" s="3">
+      <c r="C234" s="2">
         <f t="shared" si="65"/>
         <v>0.83240000000000003</v>
       </c>
@@ -58617,10 +58641,10 @@
       <c r="A235" t="s">
         <v>62</v>
       </c>
-      <c r="B235" s="9">
+      <c r="B235" s="8">
         <v>1.242</v>
       </c>
-      <c r="C235" s="3">
+      <c r="C235" s="2">
         <f t="shared" si="65"/>
         <v>0.43190000000000006</v>
       </c>
@@ -58727,10 +58751,10 @@
       <c r="A236" t="s">
         <v>63</v>
       </c>
-      <c r="B236" s="9">
+      <c r="B236" s="8">
         <v>0.84399999999999997</v>
       </c>
-      <c r="C236" s="3">
+      <c r="C236" s="2">
         <f t="shared" si="65"/>
         <v>0.25279999999999997</v>
       </c>
@@ -58837,10 +58861,10 @@
       <c r="A237" t="s">
         <v>64</v>
       </c>
-      <c r="B237" s="9">
+      <c r="B237" s="8">
         <v>1.724</v>
       </c>
-      <c r="C237" s="3">
+      <c r="C237" s="2">
         <f t="shared" si="65"/>
         <v>0.64880000000000004</v>
       </c>
@@ -58947,10 +58971,10 @@
       <c r="A238" t="s">
         <v>65</v>
       </c>
-      <c r="B238" s="9">
+      <c r="B238" s="8">
         <v>0.79200000000000004</v>
       </c>
-      <c r="C238" s="3">
+      <c r="C238" s="2">
         <f t="shared" si="65"/>
         <v>0.22940000000000005</v>
       </c>
@@ -59057,10 +59081,10 @@
       <c r="A239" t="s">
         <v>66</v>
       </c>
-      <c r="B239" s="9">
+      <c r="B239" s="8">
         <v>2.359</v>
       </c>
-      <c r="C239" s="3">
+      <c r="C239" s="2">
         <f t="shared" si="65"/>
         <v>0.93454999999999999</v>
       </c>
@@ -59167,10 +59191,10 @@
       <c r="A240" t="s">
         <v>67</v>
       </c>
-      <c r="B240" s="9">
+      <c r="B240" s="8">
         <v>0.747</v>
       </c>
-      <c r="C240" s="3">
+      <c r="C240" s="2">
         <f t="shared" si="65"/>
         <v>0.20915</v>
       </c>
@@ -59277,10 +59301,10 @@
       <c r="A241" t="s">
         <v>68</v>
       </c>
-      <c r="B241" s="9">
+      <c r="B241" s="8">
         <v>1.18</v>
       </c>
-      <c r="C241" s="3">
+      <c r="C241" s="2">
         <f t="shared" si="65"/>
         <v>0.40400000000000003</v>
       </c>
@@ -59387,10 +59411,10 @@
       <c r="A242" t="s">
         <v>69</v>
       </c>
-      <c r="B242" s="9">
+      <c r="B242" s="8">
         <v>1.097</v>
       </c>
-      <c r="C242" s="3">
+      <c r="C242" s="2">
         <f t="shared" si="65"/>
         <v>0.36664999999999998</v>
       </c>
@@ -59497,10 +59521,10 @@
       <c r="A243" t="s">
         <v>70</v>
       </c>
-      <c r="B243" s="9">
+      <c r="B243" s="8">
         <v>1.746</v>
       </c>
-      <c r="C243" s="3">
+      <c r="C243" s="2">
         <f t="shared" si="65"/>
         <v>0.65870000000000006</v>
       </c>
@@ -59607,10 +59631,10 @@
       <c r="A244" t="s">
         <v>71</v>
       </c>
-      <c r="B244" s="9">
+      <c r="B244" s="8">
         <v>1.2929999999999999</v>
       </c>
-      <c r="C244" s="3">
+      <c r="C244" s="2">
         <f t="shared" si="65"/>
         <v>0.45484999999999998</v>
       </c>
@@ -59717,10 +59741,10 @@
       <c r="A245" t="s">
         <v>72</v>
       </c>
-      <c r="B245" s="9">
+      <c r="B245" s="8">
         <v>1.0189999999999999</v>
       </c>
-      <c r="C245" s="3">
+      <c r="C245" s="2">
         <f t="shared" si="65"/>
         <v>0.33154999999999996</v>
       </c>
@@ -59825,11 +59849,11 @@
     </row>
     <row r="246" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A246" s="1"/>
-      <c r="C246" s="3"/>
+      <c r="C246" s="2"/>
     </row>
     <row r="247" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A247" s="1"/>
-      <c r="C247" s="3"/>
+      <c r="C247" s="2"/>
     </row>
     <row r="249" spans="1:29" x14ac:dyDescent="0.35">
       <c r="B249">
@@ -60096,17 +60120,17 @@
       <c r="T3">
         <v>1</v>
       </c>
-      <c r="U3" s="6">
+      <c r="U3" s="5">
         <v>138199.87</v>
       </c>
-      <c r="V3" s="5">
+      <c r="V3" s="4">
         <v>53805007711608.5</v>
       </c>
-      <c r="W3" s="6">
+      <c r="W3" s="5">
         <f>U3/(24*3600)</f>
         <v>1.5995355324074074</v>
       </c>
-      <c r="X3" s="5">
+      <c r="X3" s="4">
         <f>V3/(24*3600)</f>
         <v>622743144.81028354</v>
       </c>
@@ -60145,17 +60169,17 @@
       <c r="T4">
         <v>2</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="5">
         <v>193968.86</v>
       </c>
-      <c r="V4" s="5">
+      <c r="V4" s="4">
         <v>75493510169667</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="5">
         <f t="shared" ref="W4:W15" si="0">U4/(24*3600)</f>
         <v>2.2450099537037036</v>
       </c>
-      <c r="X4" s="5">
+      <c r="X4" s="4">
         <f t="shared" ref="X4:X15" si="1">V4/(24*3600)</f>
         <v>873767478.81559026</v>
       </c>
@@ -60194,17 +60218,17 @@
       <c r="T5">
         <v>3</v>
       </c>
-      <c r="U5" s="6">
+      <c r="U5" s="5">
         <v>69557.14</v>
       </c>
-      <c r="V5" s="4">
+      <c r="V5" s="3">
         <v>27109914948957.199</v>
       </c>
-      <c r="W5" s="6">
+      <c r="W5" s="5">
         <f t="shared" si="0"/>
         <v>0.80505949074074068</v>
       </c>
-      <c r="X5" s="5">
+      <c r="X5" s="4">
         <f t="shared" si="1"/>
         <v>313772163.76107872</v>
       </c>
@@ -60243,17 +60267,17 @@
       <c r="T6">
         <v>4</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="3">
         <v>72517.820000000007</v>
       </c>
-      <c r="V6" s="4">
+      <c r="V6" s="3">
         <v>28261321994600</v>
       </c>
-      <c r="W6" s="6">
+      <c r="W6" s="5">
         <f t="shared" si="0"/>
         <v>0.83932662037037042</v>
       </c>
-      <c r="X6" s="5">
+      <c r="X6" s="4">
         <f t="shared" si="1"/>
         <v>327098634.19675928</v>
       </c>
@@ -60292,17 +60316,17 @@
       <c r="T7">
         <v>5</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="3">
         <v>28498.74</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7" s="3">
         <v>11142346057363.6</v>
       </c>
-      <c r="W7" s="6">
+      <c r="W7" s="5">
         <f t="shared" si="0"/>
         <v>0.32984652777777779</v>
       </c>
-      <c r="X7" s="5">
+      <c r="X7" s="4">
         <f t="shared" si="1"/>
         <v>128962338.62689352</v>
       </c>
@@ -60341,17 +60365,17 @@
       <c r="T8">
         <v>6</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="3">
         <v>78652.990000000005</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8" s="3">
         <v>30647281766368.301</v>
       </c>
-      <c r="W8" s="6">
+      <c r="W8" s="5">
         <f t="shared" si="0"/>
         <v>0.9103355324074075</v>
       </c>
-      <c r="X8" s="5">
+      <c r="X8" s="4">
         <f t="shared" si="1"/>
         <v>354713909.33296645</v>
       </c>
@@ -60390,17 +60414,17 @@
       <c r="T9">
         <v>7</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="3">
         <v>41862.03</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="3">
         <v>16339315582852.199</v>
       </c>
-      <c r="W9" s="6">
+      <c r="W9" s="5">
         <f t="shared" si="0"/>
         <v>0.48451423611111111</v>
       </c>
-      <c r="X9" s="5">
+      <c r="X9" s="4">
         <f t="shared" si="1"/>
         <v>189112448.87560415</v>
       </c>
@@ -60439,17 +60463,17 @@
       <c r="T10">
         <v>8</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="3">
         <v>94202.84</v>
       </c>
-      <c r="V10" s="4">
+      <c r="V10" s="3">
         <v>36694605942300.703</v>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="5">
         <f t="shared" si="0"/>
         <v>1.0903106481481482</v>
       </c>
-      <c r="X10" s="5">
+      <c r="X10" s="4">
         <f t="shared" si="1"/>
         <v>424706087.295147</v>
       </c>
@@ -60488,17 +60512,17 @@
       <c r="T11">
         <v>9</v>
       </c>
-      <c r="U11" s="6">
+      <c r="U11" s="5">
         <v>126240.75</v>
       </c>
-      <c r="V11" s="4">
+      <c r="V11" s="3">
         <v>49154118331017.297</v>
       </c>
-      <c r="W11" s="6">
+      <c r="W11" s="5">
         <f t="shared" si="0"/>
         <v>1.4611197916666667</v>
       </c>
-      <c r="X11" s="5">
+      <c r="X11" s="4">
         <f t="shared" si="1"/>
         <v>568913406.60899651</v>
       </c>
@@ -60537,17 +60561,17 @@
       <c r="T12">
         <v>10</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="3">
         <v>19380.53</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12" s="3">
         <v>7596281742257.6104</v>
       </c>
-      <c r="W12" s="6">
+      <c r="W12" s="5">
         <f t="shared" si="0"/>
         <v>0.22431168981481481</v>
       </c>
-      <c r="X12" s="5">
+      <c r="X12" s="4">
         <f t="shared" si="1"/>
         <v>87919927.572426051</v>
       </c>
@@ -60583,13 +60607,13 @@
       <c r="H13">
         <v>1.4382807230064592E+16</v>
       </c>
-      <c r="U13" s="6"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="6">
+      <c r="U13" s="5"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X13" s="5">
+      <c r="X13" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -60625,13 +60649,13 @@
       <c r="H14">
         <v>1.464591672485694E+16</v>
       </c>
-      <c r="U14" s="6"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="6">
+      <c r="U14" s="5"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X14" s="5">
+      <c r="X14" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -60667,13 +60691,13 @@
       <c r="H15">
         <v>2.711371001189738E+16</v>
       </c>
-      <c r="U15" s="6"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="6">
+      <c r="U15" s="5"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X15" s="5">
+      <c r="X15" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -60712,17 +60736,17 @@
       <c r="T16" t="s">
         <v>45</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16" s="3">
         <v>152105.60999999999</v>
       </c>
-      <c r="V16" s="4">
+      <c r="V16" s="3">
         <v>174644194884333</v>
       </c>
-      <c r="W16" s="6">
+      <c r="W16" s="5">
         <f t="shared" ref="W16:W20" si="2">U16/(24*3600)</f>
         <v>1.7604815972222221</v>
       </c>
-      <c r="X16" s="5">
+      <c r="X16" s="4">
         <f t="shared" ref="X16:X20" si="3">V16/(24*3600)</f>
         <v>2021344848.1982987</v>
       </c>
@@ -60761,17 +60785,17 @@
       <c r="T17" t="s">
         <v>46</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="3">
         <v>70359.97</v>
       </c>
-      <c r="V17" s="4">
+      <c r="V17" s="3">
         <v>27422137361592.199</v>
       </c>
-      <c r="W17" s="6">
+      <c r="W17" s="5">
         <f t="shared" si="2"/>
         <v>0.81435150462962969</v>
       </c>
-      <c r="X17" s="5">
+      <c r="X17" s="4">
         <f t="shared" si="3"/>
         <v>317385849.0925023</v>
       </c>
@@ -60810,17 +60834,17 @@
       <c r="T18" t="s">
         <v>47</v>
       </c>
-      <c r="U18" s="4">
+      <c r="U18" s="3">
         <v>40607.21</v>
       </c>
-      <c r="V18" s="4">
+      <c r="V18" s="3">
         <v>15851317042146.5</v>
       </c>
-      <c r="W18" s="6">
+      <c r="W18" s="5">
         <f t="shared" si="2"/>
         <v>0.46999085648148148</v>
       </c>
-      <c r="X18" s="5">
+      <c r="X18" s="4">
         <f t="shared" si="3"/>
         <v>183464317.61743635</v>
       </c>
@@ -60859,17 +60883,17 @@
       <c r="T19" t="s">
         <v>48</v>
       </c>
-      <c r="U19" s="4">
+      <c r="U19" s="3">
         <v>113293.49</v>
       </c>
-      <c r="V19" s="4">
+      <c r="V19" s="3">
         <v>44118939635617.398</v>
       </c>
-      <c r="W19" s="6">
+      <c r="W19" s="5">
         <f t="shared" si="2"/>
         <v>1.3112672453703704</v>
       </c>
-      <c r="X19" s="5">
+      <c r="X19" s="4">
         <f t="shared" si="3"/>
         <v>510635875.41223842</v>
       </c>
@@ -60908,17 +60932,17 @@
       <c r="T20" t="s">
         <v>49</v>
       </c>
-      <c r="U20" s="4">
+      <c r="U20" s="3">
         <v>19380.53</v>
       </c>
-      <c r="V20" s="4">
+      <c r="V20" s="3">
         <v>7596281742257.6104</v>
       </c>
-      <c r="W20" s="6">
+      <c r="W20" s="5">
         <f t="shared" si="2"/>
         <v>0.22431168981481481</v>
       </c>
-      <c r="X20" s="5">
+      <c r="X20" s="4">
         <f t="shared" si="3"/>
         <v>87919927.572426051</v>
       </c>
@@ -60954,10 +60978,10 @@
       <c r="H21">
         <v>3.8604644435012088E+16</v>
       </c>
-      <c r="U21" s="6"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="4"/>
       <c r="AA21" s="1">
         <v>36911</v>
       </c>
@@ -60990,10 +61014,10 @@
       <c r="H22">
         <v>4.183465555651132E+16</v>
       </c>
-      <c r="U22" s="6"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="4"/>
       <c r="AA22" s="1">
         <v>36912</v>
       </c>
@@ -61026,10 +61050,10 @@
       <c r="H23">
         <v>4.321885221064196E+16</v>
       </c>
-      <c r="U23" s="6"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="4"/>
       <c r="AA23" s="1">
         <v>36913</v>
       </c>
@@ -61062,10 +61086,10 @@
       <c r="H24">
         <v>4.4600588316211648E+16</v>
       </c>
-      <c r="U24" s="6"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="4"/>
       <c r="AA24" s="1">
         <v>36914</v>
       </c>
@@ -61098,10 +61122,10 @@
       <c r="H25">
         <v>4.5315718844323648E+16</v>
       </c>
-      <c r="U25" s="6"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="4"/>
       <c r="AA25" s="1">
         <v>36915</v>
       </c>
@@ -61134,11 +61158,11 @@
       <c r="H26">
         <v>4.6433234327624208E+16</v>
       </c>
-      <c r="V26" s="5"/>
+      <c r="V26" s="4"/>
       <c r="W26" t="s">
         <v>44</v>
       </c>
-      <c r="X26" s="5"/>
+      <c r="X26" s="4"/>
       <c r="AA26" s="1">
         <v>36916</v>
       </c>
@@ -61171,8 +61195,8 @@
       <c r="H27">
         <v>4.6840735930936888E+16</v>
       </c>
-      <c r="V27" s="5"/>
-      <c r="X27" s="5"/>
+      <c r="V27" s="4"/>
+      <c r="X27" s="4"/>
       <c r="AA27" s="1">
         <v>36917</v>
       </c>
@@ -61205,8 +61229,8 @@
       <c r="H28">
         <v>4.8130933314170368E+16</v>
       </c>
-      <c r="V28" s="5"/>
-      <c r="X28" s="5"/>
+      <c r="V28" s="4"/>
+      <c r="X28" s="4"/>
       <c r="AA28" s="1">
         <v>36918</v>
       </c>
@@ -61239,8 +61263,8 @@
       <c r="H29">
         <v>4.8581794889848248E+16</v>
       </c>
-      <c r="V29" s="5"/>
-      <c r="X29" s="5"/>
+      <c r="V29" s="4"/>
+      <c r="X29" s="4"/>
       <c r="AA29" s="1">
         <v>36919</v>
       </c>
@@ -61273,8 +61297,8 @@
       <c r="H30">
         <v>5.0339703499613944E+16</v>
       </c>
-      <c r="V30" s="5"/>
-      <c r="X30" s="5"/>
+      <c r="V30" s="4"/>
+      <c r="X30" s="4"/>
       <c r="AA30" s="1">
         <v>36920</v>
       </c>
@@ -61307,8 +61331,8 @@
       <c r="H31">
         <v>5.5147780049106008E+16</v>
       </c>
-      <c r="V31" s="5"/>
-      <c r="X31" s="5"/>
+      <c r="V31" s="4"/>
+      <c r="X31" s="4"/>
       <c r="AA31" s="1">
         <v>36921</v>
       </c>
@@ -68588,7 +68612,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
+      <c r="A1" s="6"/>
       <c r="B1" t="s">
         <v>39</v>
       </c>
@@ -68612,7 +68636,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>36911.65625</v>
       </c>
       <c r="B2">
@@ -68638,7 +68662,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>36915.638888888891</v>
       </c>
       <c r="B3">
@@ -68664,7 +68688,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>36918.659722222219</v>
       </c>
       <c r="B4">
@@ -68690,7 +68714,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>36938.131944444445</v>
       </c>
       <c r="B5">
@@ -68716,7 +68740,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>36945.645833333336</v>
       </c>
       <c r="B6">
@@ -68742,7 +68766,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>36947.638888888891</v>
       </c>
       <c r="B7">
@@ -68768,7 +68792,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>36950.149305555555</v>
       </c>
       <c r="B8">
@@ -68794,7 +68818,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>36952.138888888891</v>
       </c>
       <c r="B9">
@@ -68820,7 +68844,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>36959.142361111109</v>
       </c>
       <c r="B10">
@@ -68846,7 +68870,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>36959.65625</v>
       </c>
       <c r="B11">
@@ -68872,7 +68896,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <v>36963.638888888891</v>
       </c>
       <c r="B12">
@@ -68898,7 +68922,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>36968.138888888891</v>
       </c>
       <c r="B13">
@@ -68924,7 +68948,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>36968.649305555555</v>
       </c>
       <c r="B14">
@@ -68950,7 +68974,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>36991.65625</v>
       </c>
       <c r="B15">
@@ -68976,7 +69000,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
+      <c r="A16" s="6">
         <v>36995.638888888891</v>
       </c>
       <c r="B16">
@@ -69002,7 +69026,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
+      <c r="A17" s="6">
         <v>37000.649305555555</v>
       </c>
       <c r="B17">
@@ -69028,7 +69052,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
+      <c r="A18" s="6">
         <v>37002.642361111109</v>
       </c>
       <c r="B18">
@@ -69054,7 +69078,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="7">
+      <c r="A19" s="6">
         <v>37007.65625</v>
       </c>
       <c r="B19">
@@ -69080,7 +69104,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
+      <c r="A20" s="6">
         <v>37009.645833333336</v>
       </c>
       <c r="B20">
@@ -69106,7 +69130,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <v>37011.638888888891</v>
       </c>
       <c r="B21">
@@ -69132,7 +69156,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="7">
+      <c r="A22" s="6">
         <v>37016.649305555555</v>
       </c>
       <c r="B22">
@@ -69158,7 +69182,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
+      <c r="A23" s="6">
         <v>37018.642361111109</v>
       </c>
       <c r="B23">
@@ -69184,7 +69208,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="7">
+      <c r="A24" s="6">
         <v>37020.631944444445</v>
       </c>
       <c r="B24">
@@ -69210,7 +69234,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="7">
+      <c r="A25" s="6">
         <v>37021.663194444445</v>
       </c>
       <c r="B25">
@@ -69236,7 +69260,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="7">
+      <c r="A26" s="6">
         <v>37023.142361111109</v>
       </c>
       <c r="B26">
@@ -69262,7 +69286,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="7">
+      <c r="A27" s="6">
         <v>37023.652777777781</v>
       </c>
       <c r="B27">
@@ -69288,7 +69312,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="7">
+      <c r="A28" s="6">
         <v>37025.135416666664</v>
       </c>
       <c r="B28">
@@ -69314,7 +69338,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="7">
+      <c r="A29" s="6">
         <v>37025.645833333336</v>
       </c>
       <c r="B29">
@@ -69340,7 +69364,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <v>37027.638888888891</v>
       </c>
       <c r="B30">
@@ -69366,7 +69390,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="7">
+      <c r="A31" s="6">
         <v>37032.649305555555</v>
       </c>
       <c r="B31">
@@ -69392,7 +69416,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="7">
+      <c r="A32" s="6">
         <v>37034.642361111109</v>
       </c>
       <c r="B32">
@@ -69418,7 +69442,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="7">
+      <c r="A33" s="6">
         <v>37037.663194444445</v>
       </c>
       <c r="B33">
@@ -69444,7 +69468,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="7">
+      <c r="A34" s="6">
         <v>37039.652777777781</v>
       </c>
       <c r="B34">
@@ -69470,7 +69494,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="7">
+      <c r="A35" s="6">
         <v>37041.645833333336</v>
       </c>
       <c r="B35">
@@ -69496,7 +69520,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="7">
+      <c r="A36" s="6">
         <v>37048.649305555555</v>
       </c>
       <c r="B36">
@@ -69522,7 +69546,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="7">
+      <c r="A37" s="6">
         <v>37053.663194444445</v>
       </c>
       <c r="B37">
@@ -69548,7 +69572,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="7">
+      <c r="A38" s="6">
         <v>37055.652777777781</v>
       </c>
       <c r="B38">
@@ -69574,7 +69598,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="7">
+      <c r="A39" s="6">
         <v>37078.65625</v>
       </c>
       <c r="B39">
@@ -69600,46 +69624,46 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C41" s="8">
+      <c r="C41" s="7">
         <f>C35-E35</f>
         <v>4916334.6689432263</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="7">
         <f>E35-D35</f>
         <v>4916334.6689432263</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="7">
         <v>10577346.3745075</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="7">
         <f>F35-H35</f>
         <v>3683725303987516</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="7">
         <f>H35-G35</f>
         <v>3683725303987518</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="7">
         <v>1.192615834728908E+16</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C42" s="8">
+      <c r="C42" s="7">
         <f>C12-E12</f>
         <v>2456487.6092429357</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <f>E12-D12</f>
         <v>2456487.6092429352</v>
       </c>
       <c r="E42">
         <v>5282794.9792068601</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="7">
         <f>F12-H12</f>
         <v>1841111838597846</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="7">
         <f>H12-G12</f>
         <v>1841111838597846.5</v>
       </c>
